--- a/docs/outputs/[기획]요구사항 정의서_사고뭉치.xlsx
+++ b/docs/outputs/[기획]요구사항 정의서_사고뭉치.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항 정의서" sheetId="1" r:id="R493ba691ebee4092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 기준" sheetId="2" r:id="R9a2e7fe238fc44c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항 정의서" sheetId="1" r:id="Rcf116b8682f0473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 기준" sheetId="2" r:id="Re9698fb0f6a74a77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -328,7 +328,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="112">
+  <x:cellXfs count="115">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
@@ -628,6 +628,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -938,7 +947,7 @@
     </x:row>
     <x:row r="2" s="50" customFormat="1" ht="25" customHeight="1">
       <x:c r="A2" s="63" t="str">
-        <x:v>2026-10-23 · v0.3 · 최초 초안 대조·보완 · 정책 차이는 검토 필요 · 작성 기준에 48개 원본 ID 연결</x:v>
+        <x:v>2026-10-26 · v0.5 · 165개 · 기획서/수집데이터 최종v4 반영 · 기존160개 ID 보존</x:v>
       </x:c>
       <x:c r="B2" s="63"/>
       <x:c r="C2" s="63"/>
@@ -1004,24 +1013,25 @@
       <x:c r="X3"/>
       <x:c r="Y3"/>
     </x:row>
-    <x:row r="4" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="4" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A4" s="75" t="str">
         <x:v>ACC01</x:v>
       </x:c>
       <x:c r="B4" s="75" t="str">
         <x:v>계정과 접근 권한</x:v>
       </x:c>
-      <x:c r="C4" s="75" t="str">
+      <x:c r="C4" s="112" t="str">
         <x:v>FFJ-01</x:v>
       </x:c>
-      <x:c r="D4" s="76" t="str">
+      <x:c r="D4" s="113" t="str">
         <x:v>이용 등록과 초기 안내</x:v>
       </x:c>
-      <x:c r="E4" s="76" t="str">
-        <x:v>처음 이용하는 사용자는 서비스 목적과 필요한 안내를 확인하고 이용 등록을 진행할 수 있어야 한다. 학생의 별도 계정 생성 여부와 필수 입력 항목은 계정 정책을 확정한 뒤 적용한다.</x:v>
-      </x:c>
-      <x:c r="F4" s="77" t="str">
-        <x:v>제안 · P01</x:v>
+      <x:c r="E4" s="113" t="str">
+        <x:v>데모 계정의 서비스 목적·가상 학생·미수집 범위를 안내한다. 12/7까지 공개 가입과 실제 아동 등록은 제공하지 않으며 상용 가입은 확장으로 보존한다.</x:v>
+      </x:c>
+      <x:c r="F4" s="114" t="str">
+        <x:v>제안 · P01
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1159,21 +1169,23 @@
 초안 REQ-ACC-002</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="13" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A13" s="75"/>
       <x:c r="B13" s="75"/>
-      <x:c r="C13" s="75" t="str">
+      <x:c r="C13" s="112" t="str">
         <x:v>FFJ-04</x:v>
       </x:c>
-      <x:c r="D13" s="76" t="str">
+      <x:c r="D13" s="113" t="str">
         <x:v>문제풀이의 전체 흐름</x:v>
       </x:c>
-      <x:c r="E13" s="76" t="str">
-        <x:v>학생은 대시보드에서 문제 선택 → 안내 확인 → 최초 답변 제출 → 되묻기 → 생각 추가 → 마무리 → 정답·예시 비교 → 돌아보기로 이어진다. 기록은 같은 학습 시도로 연결하며 되묻기 반복, 돌아보기 필수 여부와 완료 조건은 확정된 정책을 따른다.</x:v>
-      </x:c>
-      <x:c r="F13" s="77" t="str">
+      <x:c r="E13" s="113" t="str">
+        <x:v>미션 선택 → 안내·메모 → 최초 답 → 정답형/열린형 판정 → 힌트·되묻기 → 고친 답 → 마무리 → 정답/예시·전후 비교 → 돌아보기로 진행한다. 처음 맞힌 정답형의 이유 답변은 선택이며, 열린형은 이유와 보기 사실 일치를 구분한다. 학년별 되묻기 상한과 마무리 전 정답 미공개를 지킨다.</x:v>
+      </x:c>
+      <x:c r="F13" s="114" t="str">
         <x:v>핵심 · 기획 4.1
-검토 · P04</x:v>
+검토 · P04
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1264,20 +1276,21 @@
         <x:v>제안 · P07</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="19" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A19" s="75"/>
       <x:c r="B19" s="75"/>
-      <x:c r="C19" s="75" t="str">
+      <x:c r="C19" s="112" t="str">
         <x:v>FFJ-10</x:v>
       </x:c>
-      <x:c r="D19" s="76" t="str">
+      <x:c r="D19" s="113" t="str">
         <x:v>문제 등록과 공개 흐름</x:v>
       </x:c>
-      <x:c r="E19" s="76" t="str">
-        <x:v>관리자는 문제 작성 → 학년·생각 유형 및 입력 방식 지정 → 판정 기준·예시 답 등록 → 학생 화면 미리보기 → 내용 검토 → 공개 순서로 진행한다. 공개 전 필수 정보가 누락되면 사유를 안내한다.</x:v>
-      </x:c>
-      <x:c r="F19" s="77" t="str">
-        <x:v>제안 · 요청 범위</x:v>
+      <x:c r="E19" s="113" t="str">
+        <x:v>관리자는 성취기준·성취수준 선택 → LLM 초안/사람 작성 → 자동 검사 결과 확인 → 수정/반려 또는 검수 완료 → 시범 결과/허용 범위 확인 → 공개 순서로 진행한다. 생성 출처·오류 이유·시도 횟수·검수자·상태/버전을 확인하고 승인되지 않은 미션을 공개할 수 없어야 한다.</x:v>
+      </x:c>
+      <x:c r="F19" s="114" t="str">
+        <x:v>제안 · 요청 범위
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1296,26 +1309,27 @@
         <x:v>제안 · P06/P07</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="21" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A21" s="75" t="str">
         <x:v>PRB01</x:v>
       </x:c>
       <x:c r="B21" s="75" t="str">
         <x:v>문제풀이</x:v>
       </x:c>
-      <x:c r="C21" s="75" t="str">
+      <x:c r="C21" s="112" t="str">
         <x:v>FFH-01</x:v>
       </x:c>
-      <x:c r="D21" s="76" t="str">
+      <x:c r="D21" s="113" t="str">
         <x:v>학습 미션 목록 확인</x:v>
       </x:c>
-      <x:c r="E21" s="76" t="str">
-        <x:v>학생은 학년군별 미션의 제목·교과·수행 상태(시작 전·진행 중·완료)를 확인하고 선택할 수 있어야 한다. 학습 중 이전·다음 미션 이동과 현재 진행 위치를 확인할 수 있게 하며, 시연 학년·문항 수는 P03에서 별도로 정한다.</x:v>
-      </x:c>
-      <x:c r="F21" s="77" t="str">
+      <x:c r="E21" s="113" t="str">
+        <x:v>데모는 35개 미션을 제공한다. 초3~중3 서술·논술 30개(생각 유형 5 × 학년군 3 × 2)와 초1~2 고르기·받아쓰기 시범 5개를 구분하고 학년·교과·진행·검증 상태를 표시한다. 64개 확장은 이후 범위다.</x:v>
+      </x:c>
+      <x:c r="F21" s="114" t="str">
         <x:v>핵심 · 기획 1, 3.2
 검토 · P03
-초안 REQ-STU-001</x:v>
+초안 REQ-STU-001
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1353,22 +1367,23 @@
 검토 · P03</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" s="50" customFormat="1" ht="68" customHeight="1">
+    <x:row r="24" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A24" s="75"/>
       <x:c r="B24" s="75"/>
-      <x:c r="C24" s="75" t="str">
+      <x:c r="C24" s="112" t="str">
         <x:v>FFJ-13</x:v>
       </x:c>
-      <x:c r="D24" s="76" t="str">
+      <x:c r="D24" s="113" t="str">
         <x:v>서술형 답변 작성·제출</x:v>
       </x:c>
-      <x:c r="E24" s="76" t="str">
-        <x:v>학생은 서술형 글, 풀이형 단계 틀, 논술형 틀(주장·까닭 2개·반대 의견에 답하기)로 생각을 작성·제출할 수 있어야 한다. 저학년 보호자 받아쓰기는 아이의 말을 그대로 입력하고 지원 이용 여부를 별도 기록한다. 지원 학년과 입력 틀의 세부 구성은 P03에서 정한다.</x:v>
-      </x:c>
-      <x:c r="F24" s="77" t="str">
+      <x:c r="E24" s="113" t="str">
+        <x:v>초3~중3은 서술·풀이·논술(주장·까닭·반론) 입력을 지원하고 초1~2는 고르기·아이 말 그대로 보호자 받아쓰기를 제공한다. input_mode와 도움 여부를 기록하고 받아쓰기 자체를 사고력 부족으로 판정하지 않는다. STT는 데모에서 제외한다.</x:v>
+      </x:c>
+      <x:c r="F24" s="114" t="str">
         <x:v>핵심 · 기획 4.2, 6.2
 검토 · P03
-초안 REQ-STU-003, REQ-STU-004</x:v>
+초안 REQ-STU-003, REQ-STU-004
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1388,23 +1403,24 @@
 초안 REQ-STU-007</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" s="50" customFormat="1" ht="68" customHeight="1">
+    <x:row r="26" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A26" s="75"/>
       <x:c r="B26" s="75"/>
-      <x:c r="C26" s="75" t="str">
+      <x:c r="C26" s="112" t="str">
         <x:v>FFJ-15</x:v>
       </x:c>
-      <x:c r="D26" s="76" t="str">
+      <x:c r="D26" s="113" t="str">
         <x:v>생각 메모 작성</x:v>
       </x:c>
-      <x:c r="E26" s="76" t="str">
-        <x:v>학생은 메모를 작성하고 내용을 답변 칸으로 옮길 수 있어야 한다. 메모와 제출 답변을 구분한다. [검토 필요] 초안은 메모 미저장이나 현행은 자동 저장 대상을 정책으로 결정하므로, 메모 보관 여부는 P05 확정 전 임의로 적용하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F26" s="77" t="str">
+      <x:c r="E26" s="113" t="str">
+        <x:v>미션 메모를 제출 답변과 구분해 학습 시도에 저장하고 답변 칸으로 옮길 수 있게 한다. 마지막 저장 시점·충돌·복원·삭제를 SAV01과 같이 처리하며 메모는 모델 채점과 공개 리포트의 확정 답변에 섞지 않는다.</x:v>
+      </x:c>
+      <x:c r="F26" s="114" t="str">
         <x:v>핵심 · 기획 4.1
 검토 · P05, P09
 검토 필요 · P05
-초안 REQ-STU-008</x:v>
+초안 REQ-STU-008
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1439,22 +1455,23 @@
         <x:v>핵심 · 기획 1, 4.1, 6.1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" s="50" customFormat="1" ht="68" customHeight="1">
+    <x:row r="29" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A29" s="75"/>
       <x:c r="B29" s="75"/>
-      <x:c r="C29" s="75" t="str">
+      <x:c r="C29" s="112" t="str">
         <x:v>FBN-03</x:v>
       </x:c>
-      <x:c r="D29" s="76" t="str">
+      <x:c r="D29" s="113" t="str">
         <x:v>학습 마무리·정답 공개 조건</x:v>
       </x:c>
-      <x:c r="E29" s="76" t="str">
-        <x:v>학생이 확정된 학습 마무리 조건을 충족한 뒤 닫힌 문제의 정답 또는 열린 문제의 예시 답과 들어가면 좋은 생각을 확인할 수 있어야 한다. 체크리스트는 학생 답에서 근거 구절이 실제 확인된 요소만 체크하고 그 구절을 함께 표시한다.</x:v>
-      </x:c>
-      <x:c r="F29" s="77" t="str">
+      <x:c r="E29" s="113" t="str">
+        <x:v>마무리 전 정답·예시 답을 노출하지 않는다. 닫힌 문항의 키 대조·힌트 후 종료와 열린 문항의 요소·이유 확인을 구분하고 마무리 후 처음·마지막 답과 근거 구절·예시를 제시한다. 이유가 다른 열린 답을 단순 오답으로 처리하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F29" s="114" t="str">
         <x:v>핵심 · 기획 3.2, 4.1
 검토 · P04
-초안 REQ-STU-011, REQ-STU-012</x:v>
+초안 REQ-STU-011, REQ-STU-012
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1545,74 +1562,78 @@
         <x:v>핵심 · 기획 1, 4.1</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="35" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A35" s="75"/>
       <x:c r="B35" s="75"/>
-      <x:c r="C35" s="75" t="str">
+      <x:c r="C35" s="112" t="str">
         <x:v>FBF-09</x:v>
       </x:c>
-      <x:c r="D35" s="76" t="str">
+      <x:c r="D35" s="113" t="str">
         <x:v>고르기·최종 답 판정</x:v>
       </x:c>
-      <x:c r="E35" s="76" t="str">
-        <x:v>고르기는 정답 키로 확인하고 다른 답에는 까닭을 묻는다. 저학년 이유 설명 자체는 판정하지 않는다. 수학 최종 답은 분수·소수·한글 분수 등 동치 표현을 같은 답으로 확인하며, 이 규칙으로 풀이 과정을 판정하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F35" s="77" t="str">
+      <x:c r="E35" s="113" t="str">
+        <x:v>정답형은 answer_key로 최초 답과 힌트 후 답을 대조해 처음 맞힘·힌트 후 맞힘·다시 풀기를 구분한다. 열린형은 선택 자체 대신 이유 제시와 보기 사실 일치를 따로 확인한다. 초1~2 결과는 점수 없이 학부모 기록으로 제공한다. 수학 동치 최종 답 규칙으로 풀이 과정을 판정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F35" s="114" t="str">
         <x:v>핵심 · 기획 4.1
-초안 REQ-JDG-001, REQ-JDG-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" s="50" customFormat="1" ht="68" customHeight="1">
+초안 REQ-JDG-001, REQ-JDG-002
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A36" s="75"/>
       <x:c r="B36" s="75"/>
-      <x:c r="C36" s="75" t="str">
+      <x:c r="C36" s="112" t="str">
         <x:v>FAC-01</x:v>
       </x:c>
-      <x:c r="D36" s="76" t="str">
+      <x:c r="D36" s="113" t="str">
         <x:v>서술 답변 근거 확인</x:v>
       </x:c>
-      <x:c r="E36" s="76" t="str">
-        <x:v>서술·논술에서 LLM은 기준표 요소에 해당하는 구절을 찾고 코드는 원문 일치 여부를 확인하여 요소·배점 기준으로 정답·부분 정답·다시 생각을 판정한다. 근거 없는 요소는 충족으로 표시하지 않고 검증 전에는 AI 채점(시범)임을 구분하며 숫자 레벨은 노출하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F36" s="77" t="str">
+      <x:c r="E36" s="113" t="str">
+        <x:v>서술·논술의 생각 요소는 미션별 2~3개의 있음·없음과 원문 근거로 판정한다. LLM이 구절을 찾고 코드가 실재를 대조한다. 닫힌 문항 정답 키, M2의 8항목 1~5점, 생각 요소는 별도 결과다. 평가 승인 미션·학년군만 충족 판정을 제공하고 나머지는 기록·근거 및 보류 상태를 제공한다.</x:v>
+      </x:c>
+      <x:c r="F36" s="114" t="str">
         <x:v>핵심 · 기획 1, 4.1
 검토 · P08
-초안 REQ-JDG-003, REQ-JDG-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-JDG-003, REQ-JDG-005
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A37" s="75"/>
       <x:c r="B37" s="75"/>
-      <x:c r="C37" s="75" t="str">
+      <x:c r="C37" s="112" t="str">
         <x:v>FAC-02</x:v>
       </x:c>
-      <x:c r="D37" s="76" t="str">
+      <x:c r="D37" s="113" t="str">
         <x:v>근거 부족 시 판정 보류</x:v>
       </x:c>
-      <x:c r="E37" s="76" t="str">
-        <x:v>근거 부족·인용 불일치·짧은 답변·미검증 학년/문항 조합은 낮은 수준으로 기록하지 않고 판정을 보류한다. 초1~2 서술 판정과 미검증 M1 수학 과정은 활성화 범위 확인 전 보류하며 API 실패는 처리 실패로 구분한다.</x:v>
-      </x:c>
-      <x:c r="F37" s="77" t="str">
+      <x:c r="E37" s="113" t="str">
+        <x:v>근거 부족·인용 불일치·짧은 답·미검증 미션·학년군·모델 불일치는 판정 보류로 처리하고 API 오류는 처리 실패로 구분한다. 미검증 범위의 점수·요소 충족을 임의로 채우지 않으며 저학년은 정답표·이유 확인 범위를 사용한다.</x:v>
+      </x:c>
+      <x:c r="F37" s="114" t="str">
         <x:v>핵심 · 기획 3.2, 4.1
-초안 REQ-JDG-006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-JDG-006
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A38" s="75"/>
       <x:c r="B38" s="75"/>
-      <x:c r="C38" s="75" t="str">
+      <x:c r="C38" s="112" t="str">
         <x:v>FAC-03</x:v>
       </x:c>
-      <x:c r="D38" s="76" t="str">
+      <x:c r="D38" s="113" t="str">
         <x:v>답변에 따른 되묻기 제공</x:v>
       </x:c>
-      <x:c r="E38" s="76" t="str">
-        <x:v>실제 답변과 기준표에 근거해 한 걸음 더·더 말해 보기·다시 살펴보기 질문을 제공한다. 정답·금지어 유출을 확인하고 질문 출처를 기록한다. [검토 필요] 1회 재생성 후 중립 질문 은행 사용 여부와 표시 방식은 P16에서 정한다.</x:v>
-      </x:c>
-      <x:c r="F38" s="77" t="str">
+      <x:c r="E38" s="113" t="str">
+        <x:v>문항 분기·답변 근거·요소에 따라 한 걸음 더·더 말해 보기·다시 살펴보기 질문을 제공하고 정답·금지어를 대조한다. 힌트는 장면 다시 보기 → 비교 질문 → 마무리 후 예시 순서를 적용한다. 재생성·질문 은행 대체는 P16에서 승인한 경우에만 출처와 실패를 명시한다.</x:v>
+      </x:c>
+      <x:c r="F38" s="114" t="str">
         <x:v>핵심 · 기획 4.1, 5.1
 검토 필요 · P16
-초안 REQ-JDG-004</x:v>
+초안 REQ-JDG-004
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1632,23 +1653,24 @@
 검토 · P04</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" s="50" customFormat="1" ht="68" customHeight="1">
+    <x:row r="40" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A40" s="75"/>
       <x:c r="B40" s="75"/>
-      <x:c r="C40" s="75" t="str">
+      <x:c r="C40" s="112" t="str">
         <x:v>FBN-04</x:v>
       </x:c>
-      <x:c r="D40" s="76" t="str">
+      <x:c r="D40" s="113" t="str">
         <x:v>되묻기 반복·종료 안내</x:v>
       </x:c>
-      <x:c r="E40" s="76" t="str">
-        <x:v>추가 답변 후 다음 질문 또는 마무리로 안내한다. [검토 필요] 초안의 모든 단계 건너뛰기(이대로 돌아보기)·고르기 정답 후 바로 돌아보기와 현행의 미정 종료 기준을 P04에서 합의한다. 확정된 조건과 현재 가능한 행동을 학생에게 안내한다.</x:v>
-      </x:c>
-      <x:c r="F40" s="77" t="str">
+      <x:c r="E40" s="113" t="str">
+        <x:v>되묻기 상한은 초1~2 1회, 초3~4 2회, 초5~중3 3회로 두고 요소 충족·학생 마무리·상한 도달을 별도 기록한다. 질문 횟수는 성공한 서로 다른 질문 기준이며 API 재시도를 추가 학습 턴으로 세지 않는다. P04의 건너뛰기 조건과 정답 공개를 함께 지킨다.</x:v>
+      </x:c>
+      <x:c r="F40" s="114" t="str">
         <x:v>제안 · P04
 근거 · 기획 4.1
 검토 필요 · P04
-초안 REQ-STU-010</x:v>
+초안 REQ-STU-010
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="50" customFormat="1" ht="57" customHeight="1">
@@ -1894,57 +1916,62 @@
         <x:v>제안 · P06, P08</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="55" s="50" customFormat="1" ht="93" customHeight="1">
       <x:c r="A55" s="75"/>
       <x:c r="B55" s="75"/>
-      <x:c r="C55" s="75" t="str">
+      <x:c r="C55" s="112" t="str">
         <x:v>FBF-16</x:v>
       </x:c>
-      <x:c r="D55" s="76" t="str">
+      <x:c r="D55" s="113" t="str">
         <x:v>리포트 수치와 계산 근거 제공</x:v>
       </x:c>
-      <x:c r="E55" s="76" t="str">
-        <x:v>리포트 수치는 코드로 계산하고 기간·분자·분모·계산식·출처 유형(기록·규칙·정답 키·AI 관찰)을 연결한다. [검토 필요] 초안의 분모 5 미만은 비율 대신 개수만 표시하는 기준을 P08에서 합의하며 작은 표본을 능력 부족으로 해석하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F55" s="77" t="str">
+      <x:c r="E55" s="113" t="str">
+        <x:v>기간·유효/제외 건수·분자/분모·계산식·출처를 연결한다. 초1~2는 표본 수에 관계없이 처음 맞힘/전체 정답형·힌트 후 맞힘/처음 틀림·이유 제시/전체 열린형을 몇 개 중 몇 개로만 표시하고 이유의 사실 일치는 별도 건수로 보인다. 다른 학년 비율은 동일 유형/학년군/기준표의 유효 5건 이상에만 표시한다.</x:v>
+      </x:c>
+      <x:c r="F55" s="114" t="str">
         <x:v>핵심 · 기획 1, 3.2, 4
 검토 필요 · P08
-초안 REQ-RPT-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-RPT-002
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" s="50" customFormat="1" ht="78" customHeight="1">
       <x:c r="A56" s="75"/>
       <x:c r="B56" s="75"/>
-      <x:c r="C56" s="75" t="str">
+      <x:c r="C56" s="112" t="str">
         <x:v>FAC-08</x:v>
       </x:c>
-      <x:c r="D56" s="76" t="str">
+      <x:c r="D56" s="113" t="str">
         <x:v>다섯 생각 유형의 기록 요약</x:v>
       </x:c>
-      <x:c r="E56" s="76" t="str">
-        <x:v>서비스는 분석하기·따져 보기·새로 만들기·문제 해결하기·돌아보기 유형에 해당하는 주간 활동을 실제 미션과 답변 근거로 요약해야 한다. 수행 기록이 없는 유형은 확인된 기록이 없음을 구분해 표시해야 한다.</x:v>
-      </x:c>
-      <x:c r="F56" s="77" t="str">
+      <x:c r="E56" s="113" t="str">
+        <x:v>다섯 생각 유형은 팀이 구성한 관찰 틀로 사용한다. 미션별 성취기준·VALUE/블룸/메타인지 참고 요소·근거 구절·평가 승인 범위를 연결하고 미관찰 유형을 능력 부족으로 보지 않는다. 대학생용 VALUE를 초·중학생 표준 검사로 표현하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F56" s="114" t="str">
         <x:v>핵심 · 기획 1
-제안 · 유형별 기록 부재 표시</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" s="50" customFormat="1" ht="57" customHeight="1">
+제안 · 유형별 기록 부재 표시
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" s="50" customFormat="1" ht="93" customHeight="1">
       <x:c r="A57" s="75"/>
       <x:c r="B57" s="75"/>
-      <x:c r="C57" s="75" t="str">
+      <x:c r="C57" s="112" t="str">
         <x:v>FAC-09</x:v>
       </x:c>
-      <x:c r="D57" s="76" t="str">
+      <x:c r="D57" s="113" t="str">
         <x:v>질문 전후 답변 변화 제시</x:v>
       </x:c>
-      <x:c r="E57" s="76" t="str">
-        <x:v>동일 학습의 받은 질문과 최초·추가 답변을 함께 제시하고 글자 수·문장 수·까닭을 잇는 말의 개수 변화를 정의된 규칙으로 계산한다. 실제로 센 값만 표시하며 이를 생각의 깊이나 사고력 향상으로 단정하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F57" s="77" t="str">
+      <x:c r="E57" s="113" t="str">
+        <x:v>처음 답 충족·되묻기 후 새 요소·논증 요소·근거/연결어 변화는 같은 유형/학년군/기준표에서 비교한다. 초1~2는 정답형 최초/힌트 후 결과와 열린형 이유/사실 일치를 분리해 건수로만 표시한다. 분모 0·처음 누락 0은 해당 없음, 미수집·보류·실패는 0점으로 채우지 않는다. 교육 효과·직접 작성 증명으로 단정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F57" s="114" t="str">
         <x:v>핵심 · 기획 1, 2.2
 검토 · P08
-초안 REQ-RPT-004</x:v>
+초안 REQ-RPT-004
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2327,56 +2354,61 @@
         <x:v>제안 · P07</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="80" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A80" s="75"/>
       <x:c r="B80" s="75"/>
-      <x:c r="C80" s="75" t="str">
+      <x:c r="C80" s="112" t="str">
         <x:v>FAD-03</x:v>
       </x:c>
-      <x:c r="D80" s="76" t="str">
+      <x:c r="D80" s="113" t="str">
         <x:v>자체 미션 작성·수정</x:v>
       </x:c>
-      <x:c r="E80" s="76" t="str">
-        <x:v>관리자는 자체 미션의 장면·질문·입력 방식·안내·학년·교과·생각 유형과 교육과정 성취기준 연결을 등록·수정한다. 시연 전용과 일반 공개 대상을 구분하고 검토·공개 상태를 관리하며 AI Hub 문항·답안·피드백 원문을 공개하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F80" s="77" t="str">
+      <x:c r="E80" s="113" t="str">
+        <x:v>모든 자체 미션은 성취기준 코드 1개 이상·성취수준·학년군/교과/행동·생각 유형·요소표에 연결한다. 35개 구성과 대표 검증 5개를 구분하고 현재 코드가 비어 있다고 보고된 MVP 10개는 코드 연결·학년 재검토 후 사용한다. 컵 물방울의 예시 코드는 검수 후보이며 자동 확정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F80" s="114" t="str">
         <x:v>제안 · P07
 근거 · 기획 1, 6
-초안 REQ-DAT-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-DAT-003
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A81" s="75"/>
       <x:c r="B81" s="75"/>
-      <x:c r="C81" s="75" t="str">
+      <x:c r="C81" s="112" t="str">
         <x:v>FAD-04</x:v>
       </x:c>
-      <x:c r="D81" s="76" t="str">
+      <x:c r="D81" s="113" t="str">
         <x:v>미션 기준·예시 답 관리</x:v>
       </x:c>
-      <x:c r="E81" s="76" t="str">
-        <x:v>관리자는 미션의 요소·배점·흔한 오답, 정답·예시 답, 들어가면 좋은 생각과 생각 열기 질문을 관리한다. 요소별 근거와 판정 결과의 연결, 공개 시점과 내용의 일치를 검토하며 기준 변경은 기존 학습 당시의 기준과 구분한다.</x:v>
-      </x:c>
-      <x:c r="F81" s="77" t="str">
+      <x:c r="E81" s="113" t="str">
+        <x:v>미션별 question_type·answer_key·단계별 hints·장면/질문·요소 2~3개·금지어·다른 정답/예시 답·성취기준·rubric_version을 관리한다. 정답형 키와 열린형 이유/보기 사실 기준을 분리하고 변경 시 과거 학습 당시 문항·기준을 보존한다.</x:v>
+      </x:c>
+      <x:c r="F81" s="114" t="str">
         <x:v>제안 · P07
 근거 · 기획 4.1, 7
-초안 REQ-JDG-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-JDG-005
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" s="50" customFormat="1" ht="93" customHeight="1">
       <x:c r="A82" s="75"/>
       <x:c r="B82" s="75"/>
-      <x:c r="C82" s="75" t="str">
+      <x:c r="C82" s="112" t="str">
         <x:v>FBN-09</x:v>
       </x:c>
-      <x:c r="D82" s="76" t="str">
+      <x:c r="D82" s="113" t="str">
         <x:v>미션 검토·게시</x:v>
       </x:c>
-      <x:c r="E82" s="76" t="str">
-        <x:v>관리자는 미션의 질문, 학년 적합성, 기준표와 정답 공개 조건을 검토한 뒤 게시할 수 있어야 한다. 필수 내용이 누락된 미션은 게시할 수 없는 이유를 확인하며, 검토 완료와 게시 가능 여부를 결정할 담당 역할은 운영 정책으로 정한다.</x:v>
-      </x:c>
-      <x:c r="F82" s="77" t="str">
-        <x:v>제안 · P07</x:v>
+      <x:c r="E82" s="113" t="str">
+        <x:v>생성 초안은 필수값·성취기준 코드 실재·정답/금지어 누출·학년별 질문 길이를 자동 검사한 뒤 김동섭이 승인·수정·반려한다. source와 draft→reviewed→published 상태를 기록하고 자동 검사 통과만으로 공개하지 않는다. 시범 풀이/검수 미달은 보류하며 기존 제공 중단은 비공개 상태로 보존한다.</x:v>
+      </x:c>
+      <x:c r="F82" s="114" t="str">
+        <x:v>제안 · P07
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="83" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2412,59 +2444,64 @@
         <x:v>제안 · P07</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" s="50" customFormat="1" ht="57" customHeight="1">
+    <x:row r="85" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A85" s="75" t="str">
         <x:v>COM01</x:v>
       </x:c>
       <x:c r="B85" s="75" t="str">
         <x:v>공통 기록과 표현 기준</x:v>
       </x:c>
-      <x:c r="C85" s="75" t="str">
+      <x:c r="C85" s="112" t="str">
         <x:v>FAD-05</x:v>
       </x:c>
-      <x:c r="D85" s="76" t="str">
+      <x:c r="D85" s="113" t="str">
         <x:v>생각 유형 기준 통일</x:v>
       </x:c>
-      <x:c r="E85" s="76" t="str">
-        <x:v>문제·대화·대시보드·리포트는 분석하기·따져 보기·새로 만들기·문제 해결하기·돌아보기의 다섯 유형을 동일하게 사용한다. 비교·분류·순서·규칙·원인과 결과·추론은 기초 사고력으로 구분한다.</x:v>
-      </x:c>
-      <x:c r="F85" s="77" t="str">
-        <x:v>핵심 · 기획 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" s="50" customFormat="1" ht="68" customHeight="1">
+      <x:c r="E85" s="113" t="str">
+        <x:v>다섯 생각 유형은 팀이 구성한 관찰 틀로 일관되게 사용한다. 유형·학년·교과·성취기준/성취수준·행동 동사의 연결을 관리한다. 문서상 수집 완료 790개는 수집본 정리/원문 대조/서비스 적재/미션 태깅 완료와 구분하며 분류 자체를 표준 검사로 표현하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F85" s="114" t="str">
+        <x:v>핵심 · 기획 1
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" s="50" customFormat="1" ht="85" customHeight="1">
       <x:c r="A86" s="75"/>
       <x:c r="B86" s="75"/>
-      <x:c r="C86" s="75" t="str">
+      <x:c r="C86" s="112" t="str">
         <x:v>FAC-11</x:v>
       </x:c>
-      <x:c r="D86" s="76" t="str">
+      <x:c r="D86" s="113" t="str">
         <x:v>학습 모델 결과의 사용 조건</x:v>
       </x:c>
-      <x:c r="E86" s="76" t="str">
-        <x:v>평가 기준을 통과한 학년·문항·요소에만 모델을 활성화한다. M2 항목 점수는 AI 관찰로 구분하고 LLM 관찰과 불일치하면 보류한다. M1은 승인된 확신도 미만일 때 보류하고 실수 위치는 표시하지 않는다. 검증 전 숫자 레벨은 숨기며 임시 확신도 0.8의 채택 여부는 P15에서 정한다.</x:v>
-      </x:c>
-      <x:c r="F86" s="77" t="str">
+      <x:c r="E86" s="113" t="str">
+        <x:v>초5~중3 M2는 평가와 모델 사용조건을 모두 통과한 범위만 사용한다. 초3~4는 LLM 근거 관찰, 초1~2는 정답표/이유 확인과 건수 기록을 제공한다. 점수·요소·관찰 불일치는 보류하고 미확인 모델·미검증 미션은 활성화하지 않는다. M1·sLLM 미도입이 핵심 흐름을 막지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="F86" s="114" t="str">
         <x:v>핵심 · 기획 1/5.2
 검토 필요 · P15
-초안 REQ-JDG-007, REQ-JDG-008</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" s="50" customFormat="1" ht="57" customHeight="1">
+초안 REQ-JDG-007, REQ-JDG-008
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" s="50" customFormat="1" ht="93" customHeight="1">
       <x:c r="A87" s="75"/>
       <x:c r="B87" s="75"/>
-      <x:c r="C87" s="75" t="str">
+      <x:c r="C87" s="112" t="str">
         <x:v>FBN-11</x:v>
       </x:c>
-      <x:c r="D87" s="76" t="str">
+      <x:c r="D87" s="113" t="str">
         <x:v>시연 데이터와 외부 전달 범위</x:v>
       </x:c>
-      <x:c r="E87" s="76" t="str">
-        <x:v>시연은 가상 학생과 자체 미션을 사용하고 실제 아동 정보·음성을 수집하지 않으며 학생 이름은 외부 API에 보내지 않는다. AI Hub 원본·가공본·EDA 예시는 저장소와 서비스 화면에 포함하지 않고 Claude 등 생성형 AI 출력은 모델 학습 자료로 사용하지 않는다.</x:v>
-      </x:c>
-      <x:c r="F87" s="77" t="str">
+      <x:c r="E87" s="113" t="str">
+        <x:v>데모는 가상 학생·자체 미션만 사용하고 실제 아동 가입/정보/음성·STT 수집은 제공하지 않는다. 실명·불필요한 식별정보는 외부 AI에 보내지 않고 원문 키/클립보드 내용은 저장하지 않는다. Claude 출력은 모델 학습에 사용하지 않는 팀 원칙을 지키며, 미션 초안 생성과 모델 학습 데이터는 별도로 관리한다.</x:v>
+      </x:c>
+      <x:c r="F87" s="114" t="str">
         <x:v>핵심 · 기획 6/6.2
-초안 REQ-SEC-001, REQ-SEC-003</x:v>
+초안 REQ-SEC-001, REQ-SEC-003
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="88" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2610,27 +2647,28 @@
 연계 · NTF01</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" s="50" customFormat="1" ht="68" customHeight="1">
-      <x:c r="A96" s="101" t="str">
+    <x:row r="96" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A96" s="75" t="str">
         <x:v>SAV01</x:v>
       </x:c>
-      <x:c r="B96" s="101" t="str">
+      <x:c r="B96" s="75" t="str">
         <x:v>초안 자동 저장과 복원</x:v>
       </x:c>
-      <x:c r="C96" s="101" t="str">
+      <x:c r="C96" s="112" t="str">
         <x:v>FBF-24</x:v>
       </x:c>
-      <x:c r="D96" s="102" t="str">
+      <x:c r="D96" s="113" t="str">
         <x:v>작성 중 초안 자동 저장</x:v>
       </x:c>
-      <x:c r="E96" s="102" t="str">
-        <x:v>학생의 답변 초안을 학생·문제·학습 시도에 연결해 자동 저장하고 제출 답변·완료 학습과 구분한다. [검토 필요] 메모는 초안에서 미저장이었으므로 P05의 보관 결정 후에만 자동 저장 대상에 포함하며 저장 시점·보존 범위를 안내한다.</x:v>
-      </x:c>
-      <x:c r="F96" s="103" t="str">
+      <x:c r="E96" s="113" t="str">
+        <x:v>답변 초안과 생각 메모를 학습 시도·사용자·미션에 연결해 저장하고 제출 답변과 구분한다. 저장 시점·버전·실패·동시 편집 충돌·마지막 복원 범위와 보존·삭제를 같이 관리하며 실패를 저장 완료로 표시하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F96" s="114" t="str">
         <x:v>우선 1 · 추가 요청
 검토 · P05/P09
 검토 필요 · P05
-초안 REQ-STU-008</x:v>
+초안 REQ-STU-008
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2689,22 +2727,23 @@
 초안 REQ-QA-001</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A100" s="101"/>
-      <x:c r="B100" s="101"/>
-      <x:c r="C100" s="101" t="str">
+    <x:row r="100" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A100" s="75"/>
+      <x:c r="B100" s="75"/>
+      <x:c r="C100" s="112" t="str">
         <x:v>FAR-02</x:v>
       </x:c>
-      <x:c r="D100" s="102" t="str">
+      <x:c r="D100" s="113" t="str">
         <x:v>판정과 설명의 품질 평가</x:v>
       </x:c>
-      <x:c r="E100" s="102" t="str">
-        <x:v>초안 기준인 미션당 예시 답안 20~30개와 평가자 2명의 독립 채점을 검토 기준으로 두고 실제 표본 수는 P11에서 확정한다. 사람-사람·사람-AI 일치도를 비교하고 검증 통과 요소만 충족으로 표시한다. 데이터·버전을 기록하고 모델별 지표는 MDL01에 따른다.</x:v>
-      </x:c>
-      <x:c r="F100" s="103" t="str">
+      <x:c r="E100" s="113" t="str">
+        <x:v>대표 미션 5개 × 20개 답안 100개는 사람 2인이 같은 요소표로 독립 판정한다. 생각 요소는 카파, M2 동일 8항목 1~5점은 QWK로 구분한다. 전문가 답안 30~50개로 채점 기준을 보정하고 충분히 일치하지 않으면 M2 검증은 AI Hub 전문가 평가셋만 사용한다. 결과는 해당 미션·학년군 범위에 한정한다.</x:v>
+      </x:c>
+      <x:c r="F100" s="114" t="str">
         <x:v>우선 1 · 추가 요청
 기획 5.2/6.1 · P08
-초안 REQ-DAT-002</x:v>
+초안 REQ-DAT-002
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2724,20 +2763,21 @@
 검토 · P11/P12</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A102" s="101"/>
-      <x:c r="B102" s="101"/>
-      <x:c r="C102" s="101" t="str">
+    <x:row r="102" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A102" s="75"/>
+      <x:c r="B102" s="75"/>
+      <x:c r="C102" s="112" t="str">
         <x:v>FAR-04</x:v>
       </x:c>
-      <x:c r="D102" s="102" t="str">
+      <x:c r="D102" s="113" t="str">
         <x:v>결제와 권한의 연결 검증</x:v>
       </x:c>
-      <x:c r="E102" s="102" t="str">
+      <x:c r="E102" s="113" t="str">
         <x:v>테스트 결제로 승인·실패·중복 통지·갱신 실패·해지·환불 경로를 검증해야 한다. 결제 결과와 대상 자녀의 이용 권한이 일치하는지 확인하고 모의 시험·PG 테스트·실결제 검증을 구분해 기록한다.</x:v>
       </x:c>
-      <x:c r="F102" s="103" t="str">
-        <x:v>우선 1 · 추가 요청
+      <x:c r="F102" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 1 · 추가 요청
 검토 · P13/P14</x:v>
       </x:c>
     </x:row>
@@ -2779,21 +2819,22 @@
 검토 · P11</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A105" s="101"/>
-      <x:c r="B105" s="101"/>
-      <x:c r="C105" s="101" t="str">
+    <x:row r="105" s="50" customFormat="1" ht="85" customHeight="1">
+      <x:c r="A105" s="75"/>
+      <x:c r="B105" s="75"/>
+      <x:c r="C105" s="112" t="str">
         <x:v>FAD-06</x:v>
       </x:c>
-      <x:c r="D105" s="102" t="str">
+      <x:c r="D105" s="113" t="str">
         <x:v>학년별 이용 안내</x:v>
       </x:c>
-      <x:c r="E105" s="102" t="str">
-        <x:v>학생 안내와 질문은 지원 학년이 이해할 수 있는 길이와 표현으로 제공해야 한다. 학년별 입력 부담과 버튼 문구를 대표 학습 시나리오에서 확인하고 이용이 어려운 지점을 개선 과제로 남긴다.</x:v>
-      </x:c>
-      <x:c r="F105" s="103" t="str">
+      <x:c r="E105" s="113" t="str">
+        <x:v>지원 학년이 이해할 수 있는 길이·표현·과정 단서로 안내한다. 정답형 오류에는 단서와 다시 선택할 행동을 주고 열린형의 다른 이유는 단순 오답으로 처리하지 않는다. 막연한 칭찬·능력 등급 대신 실제 답의 잘한 점을 짚으며 학년별 질문 길이는 P19에서 확정한다.</x:v>
+      </x:c>
+      <x:c r="F105" s="114" t="str">
         <x:v>우선 1 · 추가 요청
-검토 · P03/P11</x:v>
+검토 · P03/P11
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="106" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2903,21 +2944,23 @@
 검토 · P12/P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A112" s="101"/>
-      <x:c r="B112" s="101"/>
-      <x:c r="C112" s="101" t="str">
+    <x:row r="112" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A112" s="75"/>
+      <x:c r="B112" s="75"/>
+      <x:c r="C112" s="112" t="str">
         <x:v>FBN-19</x:v>
       </x:c>
-      <x:c r="D112" s="102" t="str">
+      <x:c r="D112" s="113" t="str">
         <x:v>기록 백업과 복구 확인</x:v>
       </x:c>
-      <x:c r="E112" s="102" t="str">
-        <x:v>학습·대화·리포트·거래 이력의 백업 대상과 주기, 복구 목표를 정해야 한다. 운영자는 복구 시험에서 원본 답변과 근거 연결, 결제 상태의 정합성을 확인하며 외부 PG 상태와의 차이는 별도로 대조한다.</x:v>
-      </x:c>
-      <x:c r="F112" s="103" t="str">
+      <x:c r="E112" s="113" t="str">
+        <x:v>RDS 자동 백업은 7일 보존, 배포/마이그레이션 전 수동 스냅샷과 주 1회 S3 pg_dump는 별도 보존 기간·삭제 설정·담당을 둔다. 운영 DB 삭제 후 복원에서도 삭제 이력을 재적용하고 답변/근거/리포트 정합성·접근 권한·복구 목표를 확인한다. 수동 사본이 자동으로 7일 후 삭제된다고 가정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F112" s="114" t="str">
         <x:v>우선 1 · 추가 요청
-검토 · P09/P12</x:v>
+검토 · P09/P12
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="113" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2958,21 +3001,22 @@
 추가 요청 · P08/P12</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A115" s="101"/>
-      <x:c r="B115" s="101"/>
-      <x:c r="C115" s="101" t="str">
+    <x:row r="115" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A115" s="75"/>
+      <x:c r="B115" s="75"/>
+      <x:c r="C115" s="112" t="str">
         <x:v>FAR-05</x:v>
       </x:c>
-      <x:c r="D115" s="102" t="str">
+      <x:c r="D115" s="113" t="str">
         <x:v>모델 변경 전 평가와 승인</x:v>
       </x:c>
-      <x:c r="E115" s="102" t="str">
-        <x:v>새 모델·프롬프트·기준표를 활성화하기 전에 고정된 평가 자료로 기존 결과와 비교해야 한다. 인용·계산 정확성과 사람 검토 기준을 충족한 범위만 승인하며 학습용 문항과 평가용 문항을 분리한다.</x:v>
-      </x:c>
-      <x:c r="F115" s="103" t="str">
+      <x:c r="E115" s="113" t="str">
+        <x:v>학습 전에 기준선·허용치·고정 평가 자료·범위/버전을 합의한다. 11/22는 준비·통합 검토로 두고 최종 모델·프롬프트 활성화는 11/20~21 독립 평가와 12/4 릴리스 승인 후 통과 범위에만 허용한다. 학습·보정·최종 평가 자료를 분리한다.</x:v>
+      </x:c>
+      <x:c r="F115" s="114" t="str">
         <x:v>우선 1 · 추가 요청
-검토 · P08/P11/P12</x:v>
+검토 · P08/P11/P12
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="116" s="50" customFormat="1" ht="57" customHeight="1">
@@ -2992,21 +3036,22 @@
 검토 · P08/P12</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A117" s="101"/>
-      <x:c r="B117" s="101"/>
-      <x:c r="C117" s="101" t="str">
+    <x:row r="117" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A117" s="75"/>
+      <x:c r="B117" s="75"/>
+      <x:c r="C117" s="112" t="str">
         <x:v>FBN-22</x:v>
       </x:c>
-      <x:c r="D117" s="102" t="str">
+      <x:c r="D117" s="113" t="str">
         <x:v>AI 사용량과 비용 확인</x:v>
       </x:c>
-      <x:c r="E117" s="102" t="str">
-        <x:v>운영자는 되묻기·분석 대화·리포트별 호출량·실패·처리 지연과 비용을 확인할 수 있어야 한다. 사용 한도와 경보 기준은 정책으로 정하고 한도 도달 시 가능한 이용 범위와 제한 이유를 사용자에게 안내한다.</x:v>
-      </x:c>
-      <x:c r="F117" s="103" t="str">
+      <x:c r="E117" s="113" t="str">
+        <x:v>되묻기·분석·리포트별 모델·입출력 토큰·비용 기준과 확인일을 기록한다. 사용량 로그에는 학생 ID·답변 내용을 저장하지 않고 모델 단가·일괄 생성에 따른 비용 효과는 실측 전 단정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F117" s="114" t="str">
         <x:v>우선 1 · 추가 요청
-검토 · P12/P13</x:v>
+검토 · P12/P13
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="118" s="50" customFormat="1" ht="57" customHeight="1">
@@ -3208,360 +3253,384 @@
 검토 · P09/P10</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A129" s="101" t="str">
+    <x:row r="129" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A129" s="75" t="str">
         <x:v>PAY01</x:v>
       </x:c>
-      <x:c r="B129" s="101" t="str">
+      <x:c r="B129" s="75" t="str">
         <x:v>학부모 결제와 구독</x:v>
       </x:c>
-      <x:c r="C129" s="101" t="str">
+      <x:c r="C129" s="112" t="str">
         <x:v>FFH-19</x:v>
       </x:c>
-      <x:c r="D129" s="102" t="str">
+      <x:c r="D129" s="113" t="str">
         <x:v>상품과 구독 조건 확인</x:v>
       </x:c>
-      <x:c r="E129" s="102" t="str">
+      <x:c r="E129" s="113" t="str">
         <x:v>학부모는 결제 전에 상품 가격, 청구 주기, 이용 기능, 대상 자녀 수와 이용 기간을 확인할 수 있어야 한다. 자녀 1명 월 구독을 기획 기준안으로 두되 실제 가격·무료 범위·체험 제공 여부는 정책으로 확정한다.</x:v>
       </x:c>
-      <x:c r="F129" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F129" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 기획 3.3 · 검토 P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A130" s="101"/>
-      <x:c r="B130" s="101"/>
-      <x:c r="C130" s="101" t="str">
+    <x:row r="130" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A130" s="75"/>
+      <x:c r="B130" s="75"/>
+      <x:c r="C130" s="112" t="str">
         <x:v>FFJ-32</x:v>
       </x:c>
-      <x:c r="D130" s="102" t="str">
+      <x:c r="D130" s="113" t="str">
         <x:v>결제 대상과 구매 확인</x:v>
       </x:c>
-      <x:c r="E130" s="102" t="str">
+      <x:c r="E130" s="113" t="str">
         <x:v>인증된 학부모는 구매할 상품과 이용 대상 자녀를 확인한 뒤 결제를 요청할 수 있어야 한다. 학생과 일반 관리자는 구매자의 결제를 대신 실행하지 않으며 같은 자녀의 중복 구독 허용 여부를 확인한다.</x:v>
       </x:c>
-      <x:c r="F130" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F130" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P02/P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A131" s="101"/>
-      <x:c r="B131" s="101"/>
-      <x:c r="C131" s="101" t="str">
+    <x:row r="131" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A131" s="75"/>
+      <x:c r="B131" s="75"/>
+      <x:c r="C131" s="112" t="str">
         <x:v>FBF-30</x:v>
       </x:c>
-      <x:c r="D131" s="102" t="str">
+      <x:c r="D131" s="113" t="str">
         <x:v>결제 요청과 승인 확인</x:v>
       </x:c>
-      <x:c r="E131" s="102" t="str">
+      <x:c r="E131" s="113" t="str">
         <x:v>서비스는 상품·금액·대상 자녀·구매자를 연결한 결제 요청을 생성하고 PG의 검증된 승인 결과를 확인해야 한다. 화면 복귀만으로 결제 완료를 판단하지 않으며 요청 금액과 실제 승인 정보를 대조한다.</x:v>
       </x:c>
-      <x:c r="F131" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F131" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13 · 참고 S01</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A132" s="101"/>
-      <x:c r="B132" s="101"/>
-      <x:c r="C132" s="101" t="str">
+    <x:row r="132" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A132" s="75"/>
+      <x:c r="B132" s="75"/>
+      <x:c r="C132" s="112" t="str">
         <x:v>FBF-31</x:v>
       </x:c>
-      <x:c r="D132" s="102" t="str">
+      <x:c r="D132" s="113" t="str">
         <x:v>중복·지연 결제 결과 처리</x:v>
       </x:c>
-      <x:c r="E132" s="102" t="str">
+      <x:c r="E132" s="113" t="str">
         <x:v>같은 주문의 반복 승인 요청과 중복·지연 상태 통지는 결제나 이용 권한에 한 번만 반영해야 한다. 결과가 불명확하면 확인 중으로 표시하고 PG 상태 조회로 확인하며 무조건 다시 결제하도록 안내하지 않는다.</x:v>
       </x:c>
-      <x:c r="F132" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F132" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13 · 참고 S03</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A133" s="101"/>
-      <x:c r="B133" s="101"/>
-      <x:c r="C133" s="101" t="str">
+    <x:row r="133" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A133" s="75"/>
+      <x:c r="B133" s="75"/>
+      <x:c r="C133" s="112" t="str">
         <x:v>FBF-32</x:v>
       </x:c>
-      <x:c r="D133" s="102" t="str">
+      <x:c r="D133" s="113" t="str">
         <x:v>구독 활성화와 권한 반영</x:v>
       </x:c>
-      <x:c r="E133" s="102" t="str">
+      <x:c r="E133" s="113" t="str">
         <x:v>승인이 확인된 결제는 대상 자녀의 구독 기간과 이용 권한에 연결해야 한다. 결제는 성공했으나 권한 반영이 실패하면 복구 대상으로 기록하고 추가 청구 없이 동일 결제 기준으로 반영을 재시도한다.</x:v>
       </x:c>
-      <x:c r="F133" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F133" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A134" s="101"/>
-      <x:c r="B134" s="101"/>
-      <x:c r="C134" s="101" t="str">
+    <x:row r="134" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A134" s="75"/>
+      <x:c r="B134" s="75"/>
+      <x:c r="C134" s="112" t="str">
         <x:v>FBF-33</x:v>
       </x:c>
-      <x:c r="D134" s="102" t="str">
+      <x:c r="D134" s="113" t="str">
         <x:v>정기 청구와 자동 갱신</x:v>
       </x:c>
-      <x:c r="E134" s="102" t="str">
+      <x:c r="E134" s="113" t="str">
         <x:v>자동 갱신에 동의한 구독은 확정된 청구일과 금액으로 다음 기간의 결제를 요청한다. 갱신 청구와 결과를 거래별로 기록하고 월말·중복 실행·청구 실패 시 처리 기준을 정한다.</x:v>
       </x:c>
-      <x:c r="F134" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F134" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13 · 참고 S02</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A135" s="101"/>
-      <x:c r="B135" s="101"/>
-      <x:c r="C135" s="101" t="str">
+    <x:row r="135" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A135" s="75"/>
+      <x:c r="B135" s="75"/>
+      <x:c r="C135" s="112" t="str">
         <x:v>FFH-20</x:v>
       </x:c>
-      <x:c r="D135" s="102" t="str">
+      <x:c r="D135" s="113" t="str">
         <x:v>구독 상태와 거래 내역 조회</x:v>
       </x:c>
-      <x:c r="E135" s="102" t="str">
+      <x:c r="E135" s="113" t="str">
         <x:v>학부모는 본인의 상품, 대상 자녀, 이용 기간, 다음 결제 예정일과 결제·취소·환불 내역을 확인할 수 있어야 한다. PG가 제공하는 거래 확인 자료로 연결하고 다른 학부모의 거래는 제공하지 않는다.</x:v>
       </x:c>
-      <x:c r="F135" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F135" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13/P14</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A136" s="101"/>
-      <x:c r="B136" s="101"/>
-      <x:c r="C136" s="101" t="str">
+    <x:row r="136" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A136" s="75"/>
+      <x:c r="B136" s="75"/>
+      <x:c r="C136" s="112" t="str">
         <x:v>FFJ-33</x:v>
       </x:c>
-      <x:c r="D136" s="102" t="str">
+      <x:c r="D136" s="113" t="str">
         <x:v>결제수단 변경과 갱신 실패</x:v>
       </x:c>
-      <x:c r="E136" s="102" t="str">
+      <x:c r="E136" s="113" t="str">
         <x:v>학부모는 PG가 지원하는 절차로 결제수단을 등록·변경할 수 있어야 한다. 갱신 실패 시 재시도 일정과 이용 제한 예정 상태를 안내하고 유예 기간·재청구 횟수는 정책으로 확정한다.</x:v>
       </x:c>
-      <x:c r="F136" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F136" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A137" s="101"/>
-      <x:c r="B137" s="101"/>
-      <x:c r="C137" s="101" t="str">
+    <x:row r="137" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A137" s="75"/>
+      <x:c r="B137" s="75"/>
+      <x:c r="C137" s="112" t="str">
         <x:v>FFJ-34</x:v>
       </x:c>
-      <x:c r="D137" s="102" t="str">
+      <x:c r="D137" s="113" t="str">
         <x:v>자동 갱신 해지</x:v>
       </x:c>
-      <x:c r="E137" s="102" t="str">
+      <x:c r="E137" s="113" t="str">
         <x:v>학부모는 다음 자동 청구를 중단하도록 구독 해지를 요청할 수 있어야 한다. 해지 시점, 남은 이용 기간과 다음 청구 중단 여부를 확인하게 하고 이미 결제된 거래의 환불 요청과 구분한다.</x:v>
       </x:c>
-      <x:c r="F137" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F137" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P13/P14</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A138" s="101"/>
-      <x:c r="B138" s="101"/>
-      <x:c r="C138" s="101" t="str">
+    <x:row r="138" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A138" s="75"/>
+      <x:c r="B138" s="75"/>
+      <x:c r="C138" s="112" t="str">
         <x:v>FBF-34</x:v>
       </x:c>
-      <x:c r="D138" s="102" t="str">
+      <x:c r="D138" s="113" t="str">
         <x:v>취소·환불 요청과 반영</x:v>
       </x:c>
-      <x:c r="E138" s="102" t="str">
+      <x:c r="E138" s="113" t="str">
         <x:v>학부모는 적용 기준을 확인하고 결제 취소·환불을 요청할 수 있어야 한다. 검증된 PG 처리 결과와 환불 상태를 기록하고 이용 기간·권한에 미치는 영향을 함께 반영하며 처리 실패와 검토 중 상태를 구분한다.</x:v>
       </x:c>
-      <x:c r="F138" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F138" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P14</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A139" s="101"/>
-      <x:c r="B139" s="101"/>
-      <x:c r="C139" s="101" t="str">
+    <x:row r="139" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A139" s="75"/>
+      <x:c r="B139" s="75"/>
+      <x:c r="C139" s="112" t="str">
         <x:v>FBN-25</x:v>
       </x:c>
-      <x:c r="D139" s="102" t="str">
+      <x:c r="D139" s="113" t="str">
         <x:v>거래와 결제수단 정보 보호</x:v>
       </x:c>
-      <x:c r="E139" s="102" t="str">
+      <x:c r="E139" s="113" t="str">
         <x:v>결제수단의 민감 정보는 PG의 지원 절차로 처리하고 서비스 화면·로그에 노출하지 않아야 한다. 결제 식별값과 필요한 이용 권한만 관리하며 자동 청구용 정보의 접근·폐기는 확정된 정책으로 통제한다.</x:v>
       </x:c>
-      <x:c r="F139" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F139" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P09/P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A140" s="101" t="str">
+    <x:row r="140" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A140" s="75" t="str">
         <x:v>BIL01</x:v>
       </x:c>
-      <x:c r="B140" s="101" t="str">
+      <x:c r="B140" s="75" t="str">
         <x:v>결제 운영과 대조</x:v>
       </x:c>
-      <x:c r="C140" s="101" t="str">
+      <x:c r="C140" s="112" t="str">
         <x:v>FFH-21</x:v>
       </x:c>
-      <x:c r="D140" s="102" t="str">
+      <x:c r="D140" s="113" t="str">
         <x:v>거래와 구독 운영 조회</x:v>
       </x:c>
-      <x:c r="E140" s="102" t="str">
+      <x:c r="E140" s="113" t="str">
         <x:v>결제 운영 권한이 있는 관리자는 결제·구독 상태와 대상 자녀의 권한 반영 여부를 확인할 수 있어야 한다. 전체 관리자에게 거래 상세를 제공하지 않고 조회·환불 처리 권한을 구분한다.</x:v>
       </x:c>
-      <x:c r="F140" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F140" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P07/P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A141" s="101"/>
-      <x:c r="B141" s="101"/>
-      <x:c r="C141" s="101" t="str">
+    <x:row r="141" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A141" s="75"/>
+      <x:c r="B141" s="75"/>
+      <x:c r="C141" s="112" t="str">
         <x:v>FBF-35</x:v>
       </x:c>
-      <x:c r="D141" s="102" t="str">
+      <x:c r="D141" s="113" t="str">
         <x:v>PG 거래 상태와 정기 대조</x:v>
       </x:c>
-      <x:c r="E141" s="102" t="str">
+      <x:c r="E141" s="113" t="str">
         <x:v>운영자는 내부 거래·구독 기록과 PG의 승인·취소·환불 상태를 대조할 수 있어야 한다. 누락·중복·불일치 건은 확인 대상으로 분리하고 확인 전 정상 거래로 집계하거나 임의로 이용 권한을 부여하지 않는다.</x:v>
       </x:c>
-      <x:c r="F141" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F141" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P12/P13</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A142" s="101"/>
-      <x:c r="B142" s="101"/>
-      <x:c r="C142" s="101" t="str">
+    <x:row r="142" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A142" s="75"/>
+      <x:c r="B142" s="75"/>
+      <x:c r="C142" s="112" t="str">
         <x:v>FBF-36</x:v>
       </x:c>
-      <x:c r="D142" s="102" t="str">
+      <x:c r="D142" s="113" t="str">
         <x:v>환불 조치 승인과 이력</x:v>
       </x:c>
-      <x:c r="E142" s="102" t="str">
+      <x:c r="E142" s="113" t="str">
         <x:v>권한이 있는 관리자는 환불 요청의 대상·금액·사유를 확인하고 승인된 절차로 처리한다. 요청·승인·PG 결과와 수행자를 남기며 같은 거래의 중복 취소·초과 환불을 방지한다.</x:v>
       </x:c>
-      <x:c r="F142" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F142" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P07/P14</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A143" s="101"/>
-      <x:c r="B143" s="101"/>
-      <x:c r="C143" s="101" t="str">
+    <x:row r="143" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A143" s="75"/>
+      <x:c r="B143" s="75"/>
+      <x:c r="C143" s="112" t="str">
         <x:v>FAR-06</x:v>
       </x:c>
-      <x:c r="D143" s="102" t="str">
+      <x:c r="D143" s="113" t="str">
         <x:v>테스트 결제와 운영 전환 확인</x:v>
       </x:c>
-      <x:c r="E143" s="102" t="str">
+      <x:c r="E143" s="113" t="str">
         <x:v>운영 전환 전에 테스트 거래에서 결제 승인·실패·갱신·해지·환불과 권한 반영을 확인해야 한다. 실제 결제 도입 여부와 전환 승인 주체를 정하고 테스트 거래를 실제 결제·매출 기록과 구분한다.</x:v>
       </x:c>
-      <x:c r="F143" s="103" t="str">
-        <x:v>우선 2 · 추가 요청
+      <x:c r="F143" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+우선 2 · 추가 요청
 검토 · P11/P13/P14</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A144" s="109" t="str">
+    <x:row r="144" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A144" s="75" t="str">
         <x:v>MDL01</x:v>
       </x:c>
-      <x:c r="B144" s="109" t="str">
+      <x:c r="B144" s="75" t="str">
         <x:v>모델 학습과 설명</x:v>
       </x:c>
-      <x:c r="C144" s="109" t="str">
+      <x:c r="C144" s="112" t="str">
         <x:v>FAC-13</x:v>
       </x:c>
-      <x:c r="D144" s="110" t="str">
+      <x:c r="D144" s="113" t="str">
         <x:v>M2 점수 모델 학습·평가</x:v>
       </x:c>
-      <x:c r="E144" s="110" t="str">
-        <x:v>AI Hub 71818·71819를 사용해 글 항목 점수 모델을 학습하고 기준선·전문가 일치도와 비교한다. 지시문 단위로 학습·평가를 분리하고 QWK·균형정확도·과대/과소 판정률을 보고한다. klue/roberta는 초안 기준 후보이며 확정 범위는 P15에 따른다.</x:v>
-      </x:c>
-      <x:c r="F144" s="111" t="str">
+      <x:c r="E144" s="113" t="str">
+        <x:v>71818·71819를 지시문 그룹으로 분리하고 사용조건이 확인된 M2 후보와 xlm-roberta-base 파인튜닝 기준선을 동일 분할·전처리·지표로 비교한다. 모델 리비전·문항/답안/학습 행 수·자원·QWK/균형정확도·과대/과소 판정·선정 사유를 기록한다. 문서의 라이선스 표기를 사용 허가 확인으로 대신하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F144" s="114" t="str">
         <x:v>핵심 보완 · P08/P15
-초안 REQ-MDL-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A145" s="109"/>
-      <x:c r="B145" s="109"/>
-      <x:c r="C145" s="109" t="str">
+초안 REQ-MDL-001
+10/25 보완 · v0.4
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A145" s="75"/>
+      <x:c r="B145" s="75"/>
+      <x:c r="C145" s="112" t="str">
         <x:v>FAC-14</x:v>
       </x:c>
-      <x:c r="D145" s="110" t="str">
+      <x:c r="D145" s="113" t="str">
         <x:v>설명 sLLM 학습·평가</x:v>
       </x:c>
-      <x:c r="E145" s="110" t="str">
-        <x:v>71818 전문가 피드백을 이용해 점수에 대한 학부모용 설명 모델을 학습·평가한다. LoRA·RunPod는 초안의 후보 구성으로 두고 인용·금지어 검사와 사람 검토를 수행한다. 50개 사람 평가 표본과 일정·자원은 P11·P15에서 확정한다.</x:v>
-      </x:c>
-      <x:c r="F145" s="111" t="str">
-        <x:v>선택 보완 · P11/P15
-초안 REQ-MDL-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A146" s="109"/>
-      <x:c r="B146" s="109"/>
-      <x:c r="C146" s="109" t="str">
+      <x:c r="E145" s="113" t="str">
+        <x:v>설명 sLLM은 12/7 데모 이후 확장으로 보존한다. 채택 승인 전에는 학습·제출·설명 50개 평가를 핵심 완료 조건에 포함하지 않는다. 재도입 시 71818 피드백 이용 조건·데이터·기본 모델 비교·사람 검토·활성화 기준을 확정한다.</x:v>
+      </x:c>
+      <x:c r="F145" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+선택 보완 · P11/P15
+초안 REQ-MDL-002
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A146" s="75"/>
+      <x:c r="B146" s="75"/>
+      <x:c r="C146" s="112" t="str">
         <x:v>FAC-15</x:v>
       </x:c>
-      <x:c r="D146" s="110" t="str">
+      <x:c r="D146" s="113" t="str">
         <x:v>M1 수학 데이터·모델 실험</x:v>
       </x:c>
-      <x:c r="E146" s="110" t="str">
-        <x:v>AI Hub 71716 라벨 zip을 직접 읽고 LaTeX 텍스트를 평문화하여 문항 그룹 단위로 분할·학습·평가한다. M1은 비교 후보로 관리하고 검증된 범위만 FAC-11에 따라 활성화한다. 초안의 EDA·기준선 완료 표시는 별도 실행 증거로 확인한다.</x:v>
-      </x:c>
-      <x:c r="F146" s="111" t="str">
+      <x:c r="E146" s="113" t="str">
+        <x:v>M1은 11/1 모델 선택을 위한 비교 후보다. 71716은 원본 Training/Validation 간 문항 그룹 중복을 고려해 재분할하고 LaTeX 평문화·분할 키·설정·실험 한계를 기록한다. 11/1 이후 추가 개발·서비스 활성화는 별도 범위 결정과 검증을 거친다.</x:v>
+      </x:c>
+      <x:c r="F146" s="114" t="str">
         <x:v>선택 보완 · P08/P15
-초안 REQ-MDL-003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A147" s="109"/>
-      <x:c r="B147" s="109"/>
-      <x:c r="C147" s="109" t="str">
+초안 REQ-MDL-003
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A147" s="75"/>
+      <x:c r="B147" s="75"/>
+      <x:c r="C147" s="112" t="str">
         <x:v>FAC-16</x:v>
       </x:c>
-      <x:c r="D147" s="110" t="str">
+      <x:c r="D147" s="113" t="str">
         <x:v>M2 점수 기반 주간 설명 생성</x:v>
       </x:c>
-      <x:c r="E147" s="110" t="str">
-        <x:v>승인된 설명 모델은 M2 점수를 입력받아 학부모용 설명을 주 1회 일괄 생성할 수 있어야 한다. 인용 대조·금지어 검사를 통과한 설명만 주간 리포트에 사용하고 학생용 되묻기와 구분하며 모델 미활성·처리 실패 상태를 명시한다.</x:v>
-      </x:c>
-      <x:c r="F147" s="111" t="str">
-        <x:v>선택 보완 · P06/P15
-초안 REQ-RPT-006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" s="50" customFormat="1" ht="57" customHeight="1">
-      <x:c r="A148" s="109" t="str">
+      <x:c r="E147" s="113" t="str">
+        <x:v>승인된 점수·설명 모델의 주간 설명 생성은 확장으로 보존한다. 이번 데모 리포트는 sLLM 없이 기록·코드 산출·LLM 요약으로 완성하고 모델 미활성·실패·기록 부족을 구분한다.</x:v>
+      </x:c>
+      <x:c r="F147" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+선택 보완 · P06/P15
+초안 REQ-RPT-006
+10/25 보완 · v0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A148" s="75" t="str">
         <x:v>STU02</x:v>
       </x:c>
-      <x:c r="B148" s="109" t="str">
+      <x:c r="B148" s="75" t="str">
         <x:v>학습 보조와 자기 평가</x:v>
       </x:c>
-      <x:c r="C148" s="109" t="str">
+      <x:c r="C148" s="112" t="str">
         <x:v>FFJ-35</x:v>
       </x:c>
-      <x:c r="D148" s="110" t="str">
+      <x:c r="D148" s="113" t="str">
         <x:v>시연용 말하기·전사 확인</x:v>
       </x:c>
-      <x:c r="E148" s="110" t="str">
-        <x:v>음성 시범 모드를 제공할 경우 말하기 → STT → 전사 확인·수정 → 질문으로 이어져야 한다. 시연 계정에서 동의한 성인 팀원의 음성만 사용하고 원음은 저장하지 않으며 해당 입력은 판정하지 않는다. 실제 제공 범위는 P03에서 정한다.</x:v>
-      </x:c>
-      <x:c r="F148" s="111" t="str">
-        <x:v>선택 보완 · P03/P09
-초안 REQ-STU-005</x:v>
+      <x:c r="E148" s="113" t="str">
+        <x:v>STT 음성 입력은 데모 이후 확장으로 보존한다. 이번 데모는 고르기·보호자 받아쓰기만 제공하고 실제 아동 음성 수집·저장을 하지 않는다. 재도입 시 동의·전사 확인·입력 표시·판정 범위를 확정한다.</x:v>
+      </x:c>
+      <x:c r="F148" s="114" t="str">
+        <x:v>확장 · 12/7 데모 제외
+선택 보완 · P03/P09
+초안 REQ-STU-005
+10/25 보완 · v0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="149" s="50" customFormat="1" ht="57" customHeight="1">
@@ -3674,20 +3743,267 @@
 초안 REQ-AGT-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="156" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="157" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="158" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="159" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="160" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="161" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="162" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="163" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="164" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="165" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="166" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="167" s="50" customFormat="1" ht="15.75" customHeight="1"/>
-    <x:row r="168" s="50" customFormat="1" ht="15.75" customHeight="1"/>
+    <x:row r="155" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A155" s="75" t="str">
+        <x:v>NXT01</x:v>
+      </x:c>
+      <x:c r="B155" s="75" t="str">
+        <x:v>다음 미션 추천</x:v>
+      </x:c>
+      <x:c r="C155" s="112" t="str">
+        <x:v>FFJ-41</x:v>
+      </x:c>
+      <x:c r="D155" s="113" t="str">
+        <x:v>추천 후보 확인·선택</x:v>
+      </x:c>
+      <x:c r="E155" s="113" t="str">
+        <x:v>마무리 후 승인된 동일 유형·학년군 미션 후보 2개와 추천 이유를 확인하고 하나를 선택한다. 실제 후보가 부족하면 가능한 수만 제공하고 없는 후보를 만들지 않는다. 초1~2 시범은 후보 1개 상태를 허용한다. 선택 시 권한·공개·완료 여부를 다시 확인한다.</x:v>
+      </x:c>
+      <x:c r="F155" s="114" t="str">
+        <x:v>핵심 추가 · 기획3.10/4.2 · P17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" s="50" customFormat="1" ht="108" customHeight="1">
+      <x:c r="A156" s="75" t="str"/>
+      <x:c r="B156" s="75" t="str"/>
+      <x:c r="C156" s="112" t="str">
+        <x:v>FBF-38</x:v>
+      </x:c>
+      <x:c r="D156" s="113" t="str">
+        <x:v>추천 이유·버전 이력</x:v>
+      </x:c>
+      <x:c r="E156" s="113" t="str">
+        <x:v>recommendations의 student_id·candidates·chosen_mission_id·reason_element·created_at와 참조 학습/미션/기준표 버전을 저장한다. 같은 성취기준 안에서는 쉬운 미션에서 어려운 순서로 제시하고 요소 3회 연속 누락은 해당 유형 추천에 사용한다. 통계의 5건 기준을 난도 추천 규칙으로 쓰지 않으며 실제 후보 부족·삭제·권한 해제·후보 변경을 처리한다.</x:v>
+      </x:c>
+      <x:c r="F156" s="114" t="str">
+        <x:v>핵심 추가 · 기획4.2 · P17
+10/26 v0.5 · v4 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A157" s="75" t="str">
+        <x:v>RET01</x:v>
+      </x:c>
+      <x:c r="B157" s="75" t="str">
+        <x:v>복귀 미션</x:v>
+      </x:c>
+      <x:c r="C157" s="112" t="str">
+        <x:v>FFJ-42</x:v>
+      </x:c>
+      <x:c r="D157" s="113" t="str">
+        <x:v>중단 후 복귀 안내</x:v>
+      </x:c>
+      <x:c r="E157" s="113" t="str">
+        <x:v>7일 이상 학습 활동이 없는 가상 학생에게 진행 중 미션 이어하기를 우선 제시하고 이전 학년·유형의 승인 미션을 추천한다. 7일은 P17의 구현 계획값이며 중복 학습을 새 완료로 집계하지 않는다. 부정적 등급이나 이탈 원인을 추정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F157" s="114" t="str">
+        <x:v>핵심 추가 · 기획3.10 · P05/P17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A158" s="75" t="str">
+        <x:v>GRW01</x:v>
+      </x:c>
+      <x:c r="B158" s="75" t="str">
+        <x:v>생각 조각 성장 지도</x:v>
+      </x:c>
+      <x:c r="C158" s="112" t="str">
+        <x:v>FFH-22</x:v>
+      </x:c>
+      <x:c r="D158" s="113" t="str">
+        <x:v>활동·보완 근거 지도</x:v>
+      </x:c>
+      <x:c r="E158" s="113" t="str">
+        <x:v>실제 저장된 미션·학년군·유형·기간별 완료와 새로 확인한 요소를 생각 조각으로 표시하고 원문·질문·전후 답·돌아보기로 연결한다. 미관찰·보류·실패·삭제를 구분하며 능력 점수·진단·또래 순위는 표시하지 않는다. 비교 기준 변경과 가상 데이터임을 확인할 수 있게 한다.</x:v>
+      </x:c>
+      <x:c r="F158" s="114" t="str">
+        <x:v>핵심 추가 · 기획3.10 · P08/P17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A159" s="75" t="str">
+        <x:v>RPT03</x:v>
+      </x:c>
+      <x:c r="B159" s="75" t="str">
+        <x:v>가족 대화 지원</x:v>
+      </x:c>
+      <x:c r="C159" s="112" t="str">
+        <x:v>FAC-17</x:v>
+      </x:c>
+      <x:c r="D159" s="113" t="str">
+        <x:v>이번 주 저녁 질문</x:v>
+      </x:c>
+      <x:c r="E159" s="113" t="str">
+        <x:v>주간 리포트마다 해당 자녀·기간의 실제 미션·원문·돌아보기에 근거한 가족 대화 질문을 저장한다. 정답 대필·근거 없는 상황·자녀 혼입을 금지하고 생성 실패·기록 부족을 구분한다. 데모에는 유료 상품 차등을 적용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F159" s="114" t="str">
+        <x:v>핵심 추가 · 기획3.6/4.4 · P06/P16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A160" s="75" t="str">
+        <x:v>WRT01</x:v>
+      </x:c>
+      <x:c r="B160" s="75" t="str">
+        <x:v>쓰기 과정 집계</x:v>
+      </x:c>
+      <x:c r="C160" s="112" t="str">
+        <x:v>FBF-39</x:v>
+      </x:c>
+      <x:c r="D160" s="113" t="str">
+        <x:v>쓰기 집계 기록·복원</x:v>
+      </x:c>
+      <x:c r="E160" s="113" t="str">
+        <x:v>고친 횟수·삭제 글자 수·멈춤 횟수·붙여넣기 여부를 학습 시도·답변·세션 버전과 연결해 집계한다. 멈춤은 10초 이상 입력 중단 횟수로 계획하되 포커스 이탈·백그라운드는 제외한다. 원문 키 입력·클립보드 내용은 저장하지 않고 0과 미수집·중복 재전송·IME·받아쓰기를 구분한다. 직접 작성·표절 증명으로 쓰지 않는다.</x:v>
+      </x:c>
+      <x:c r="F160" s="114" t="str">
+        <x:v>핵심 추가 · 기획4.3/4.6 · P05/P09/P18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A161" s="75" t="str">
+        <x:v>EVA01</x:v>
+      </x:c>
+      <x:c r="B161" s="75" t="str">
+        <x:v>평가 자료·적용 범위</x:v>
+      </x:c>
+      <x:c r="C161" s="112" t="str">
+        <x:v>FAD-07</x:v>
+      </x:c>
+      <x:c r="D161" s="113" t="str">
+        <x:v>평가셋·승인 범위 관리</x:v>
+      </x:c>
+      <x:c r="E161" s="113" t="str">
+        <x:v>대표 5미션 100답안·되묻기 100~200쌍·질문 50개·리포트 20개와 가상 5~10명 4주 기록을 구분하고 출처·제작자·버전·정답/라벨·분할·미션/학년군·보정/최종 평가 구분을 관리한다. 35개 전체를 검증 완료로 표시하지 않고 미검증 미션은 판정을 보류한다.</x:v>
+      </x:c>
+      <x:c r="F161" s="114" t="str">
+        <x:v>핵심 추가 · 기획5.2/5.3·데이터1/5 · P11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A162" s="75" t="str"/>
+      <x:c r="B162" s="75" t="str"/>
+      <x:c r="C162" s="112" t="str">
+        <x:v>FAR-07</x:v>
+      </x:c>
+      <x:c r="D162" s="113" t="str">
+        <x:v>독립 판정·출력 품질 검증</x:v>
+      </x:c>
+      <x:c r="E162" s="113" t="str">
+        <x:v>김태윤·황수빈 2인이 모델·상대 결과를 보지 않고 독립 판정한다. 원판정·불일치·합의 후 라벨을 분리하고 생각 요소 카파·M2 QWK·되묻기 적절성·질문 정답/인용·리포트 문장별 오류를 따로 기록한다. 구현·설정·테스트 코드 완료 후 일괄 실행하며 미달 범위는 비활성·보류로 기록한다.</x:v>
+      </x:c>
+      <x:c r="F162" s="114" t="str">
+        <x:v>핵심 추가 · 기획5.2/5.3/7 · P11/P15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" s="50" customFormat="1" ht="78" customHeight="1">
+      <x:c r="A163" s="75" t="str"/>
+      <x:c r="B163" s="75" t="str"/>
+      <x:c r="C163" s="112" t="str">
+        <x:v>FAR-08</x:v>
+      </x:c>
+      <x:c r="D163" s="113" t="str">
+        <x:v>지표·비교·상태 경계 검증</x:v>
+      </x:c>
+      <x:c r="E163" s="113" t="str">
+        <x:v>분모 0·처음 누락 0·유효 4/5건 경계·주간 시간대·반복 제출·모델/기준표 변경·부족한 후보·삭제/권한 해제·복원·저학년 받아쓰기·미수집/0 차이를 고정 입력·기대값으로 검증한다. 유효·제외 건수를 보존하고 보류·실패를 정상 0점·0%로 숨기지 않는다.</x:v>
+      </x:c>
+      <x:c r="F163" s="114" t="str">
+        <x:v>핵심 추가 · 구현 누락 방지 · P08/P11/P18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" s="50" customFormat="1" ht="85" customHeight="1">
+      <x:c r="A164" s="75" t="str">
+        <x:v>CNT02</x:v>
+      </x:c>
+      <x:c r="B164" s="75" t="str">
+        <x:v>미션 제작·교육과정</x:v>
+      </x:c>
+      <x:c r="C164" s="112" t="str">
+        <x:v>FAD-08</x:v>
+      </x:c>
+      <x:c r="D164" s="113" t="str">
+        <x:v>성취기준·성취수준 수집본 관리</x:v>
+      </x:c>
+      <x:c r="E164" s="113" t="str">
+        <x:v>문서상 수집된 초1~중3 성취기준 790개를 출처·교육과정/수집본 버전·코드·문장·학년군·과목·행동·성취수준·이용 조건과 연결해 관리한다. 중복/누락·원문 대조·적재/태깅 상태를 구분하고 모든 미션에 실재 코드 1개 이상을 연결한다. 기존 10개 미션의 코드 공란·학년 적합성을 재검토한다.</x:v>
+      </x:c>
+      <x:c r="F164" s="114" t="str">
+        <x:v>핵심 추가 · 기획v4 6.2·데이터v4 1/3.5 · P19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A165" s="75" t="str"/>
+      <x:c r="B165" s="75" t="str"/>
+      <x:c r="C165" s="112" t="str">
+        <x:v>FAC-18</x:v>
+      </x:c>
+      <x:c r="D165" s="113" t="str">
+        <x:v>성취기준 기반 미션 초안·자동 검사</x:v>
+      </x:c>
+      <x:c r="E165" s="113" t="str">
+        <x:v>성취기준/성취수준을 입력해 장면·질문·생각 요소 2~3개·금지어·다른 정답·예시를 정해진 스키마로 생성한다. 필수값·코드 실재·정답/금지어 노출·학년별 길이를 검사하고 실패 사유와 시도 횟수를 기록한다. 승인된 상한 내에서 재생성하되 반복 실패는 반려/실패로 처리하고 자동 공개하거나 임의 내용으로 성공 처리하지 않는다.</x:v>
+      </x:c>
+      <x:c r="F165" s="114" t="str">
+        <x:v>핵심 추가 · 기획v4 6.2 · P19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A166" s="75" t="str"/>
+      <x:c r="B166" s="75" t="str"/>
+      <x:c r="C166" s="112" t="str">
+        <x:v>FAR-09</x:v>
+      </x:c>
+      <x:c r="D166" s="113" t="str">
+        <x:v>미션별 시범 풀이·공개 범위 검증</x:v>
+      </x:c>
+      <x:c r="E166" s="113" t="str">
+        <x:v>35개 미션마다 팀원 답 3~5개로 요소 추출·정답형/열린형 분기·힌트·정답 유출·종료를 확인하고 개정/보류 결과를 기록한다. 총 105~175개 입력은 시범 계획이며 대표 5미션 100답안의 독립 카파 평가와 구분한다. 시범 통과가 전체 학년/미션의 판정 타당성 승인을 뜻하지 않으며 미달은 수정/보류한다.</x:v>
+      </x:c>
+      <x:c r="F166" s="114" t="str">
+        <x:v>핵심 추가 · 기획v4 6.2 · P11/P19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" s="50" customFormat="1" ht="108" customHeight="1">
+      <x:c r="A167" s="75" t="str">
+        <x:v>JDG02</x:v>
+      </x:c>
+      <x:c r="B167" s="75" t="str">
+        <x:v>정답형 결과·힌트 기록</x:v>
+      </x:c>
+      <x:c r="C167" s="112" t="str">
+        <x:v>FBF-40</x:v>
+      </x:c>
+      <x:c r="D167" s="113" t="str">
+        <x:v>정답형 결과·힌트·저학년 건수 보존</x:v>
+      </x:c>
+      <x:c r="E167" s="113" t="str">
+        <x:v>observations.choice_result·hint_step을 학습 시도/최초·수정 답/미션 버전과 연결해 처음 맞힘·힌트 후 맞힘·다시 풀기를 보존한다. 초1~2의 처음 맞힌 수/정답형 수, 힌트 후 맞힌 수/처음 틀린 수, 이유 제시 수/열린형 수와 보기 사실 일치 수를 분리한다. 분모 0·중복 요청·미수집을 구분하고 학부모에게 %·점수·등급·또래 비교 없이 건수만 제공한다.</x:v>
+      </x:c>
+      <x:c r="F167" s="114" t="str">
+        <x:v>핵심 추가 · 데이터v4 3.1/3.5 · P08/P20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" s="50" customFormat="1" ht="93" customHeight="1">
+      <x:c r="A168" s="75" t="str">
+        <x:v>MDL02</x:v>
+      </x:c>
+      <x:c r="B168" s="75" t="str">
+        <x:v>모델 사용조건 관리</x:v>
+      </x:c>
+      <x:c r="C168" s="112" t="str">
+        <x:v>FBN-26</x:v>
+      </x:c>
+      <x:c r="D168" s="113" t="str">
+        <x:v>후보 모델 사용조건·학습/배포 통제</x:v>
+      </x:c>
+      <x:c r="E168" s="113" t="str">
+        <x:v>klue/roberta·xlm-roberta-base 등 후보별 모델 카드·가중치/원저장소·리비전·학습/배포 조건·확인일·확인자·허용/미확인 범위를 기록한다. 문서의 라이선스 주장을 확인 완료로 복사하지 않으며 조건 미확인 후보는 학습/배포/활성화를 보류한다. 조건을 확인한 대체 후보와 동일 기준선 비교 결과로 선정한다.</x:v>
+      </x:c>
+      <x:c r="F168" s="114" t="str">
+        <x:v>핵심 추가 · 기획v4 5/5.2 · P15/P21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="169" s="50" customFormat="1" ht="15.75" customHeight="1"/>
     <x:row r="170" s="50" customFormat="1" ht="15.75" customHeight="1"/>
     <x:row r="171" s="50" customFormat="1" ht="15.75" customHeight="1"/>
@@ -4567,6 +4883,12 @@
     <x:mergeCell ref="B144:B147"/>
     <x:mergeCell ref="A148:A152"/>
     <x:mergeCell ref="B148:B152"/>
+    <x:mergeCell ref="A155:A156"/>
+    <x:mergeCell ref="B155:B156"/>
+    <x:mergeCell ref="A161:A163"/>
+    <x:mergeCell ref="B161:B163"/>
+    <x:mergeCell ref="A164:A166"/>
+    <x:mergeCell ref="B164:B166"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4590,7 +4912,7 @@
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="79" t="str">
-        <x:v>사고뭉치 v0.3</x:v>
+        <x:v>사고뭉치 v0.5 · 2026-10-26</x:v>
       </x:c>
       <x:c r="B2" s="79"/>
       <x:c r="C2" s="79"/>
@@ -4606,7 +4928,7 @@
         <x:v>의미</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="42" customHeight="1">
+    <x:row r="4" ht="55" customHeight="1">
       <x:c r="A4" s="90" t="str">
         <x:v>문서 상태</x:v>
       </x:c>
@@ -4617,7 +4939,7 @@
         <x:v>모든 항목은 팀 검토를 위한 요구사항 초안이다. 핵심 표기는 기획서의 중심 요구를 뜻하며 승인·구현·검증 완료를 뜻하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+    <x:row r="5" ht="55" customHeight="1">
       <x:c r="A5" s="90" t="str">
         <x:v>용어</x:v>
       </x:c>
@@ -4628,7 +4950,7 @@
         <x:v>문제는 기획서의 미션을 뜻한다. 학생 대화는 문제 안의 되묻기, 학부모 대화는 자녀 기록에 대한 분석 질의로 구분한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+    <x:row r="6" ht="55" customHeight="1">
       <x:c r="A6" s="90" t="str">
         <x:v>상세 설명</x:v>
       </x:c>
@@ -4639,7 +4961,7 @@
         <x:v>사용자 또는 시작 조건, 서비스의 동작, 완료 결과와 주요 예외를 기술한다. API·DB·프레임워크 선택은 후속 설계에서 정한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="31" customHeight="1">
+    <x:row r="7" ht="55" customHeight="1">
       <x:c r="A7" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4650,7 +4972,7 @@
         <x:v>화면에 제공해야 할 정보와 구성 요구사항. 원본 양식의 분류 체계를 유지한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="31" customHeight="1">
+    <x:row r="8" ht="55" customHeight="1">
       <x:c r="A8" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4661,7 +4983,7 @@
         <x:v>사용자 상호작용과 학생·학부모·관리자의 이용 흐름.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="31" customHeight="1">
+    <x:row r="9" ht="55" customHeight="1">
       <x:c r="A9" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4672,7 +4994,7 @@
         <x:v>업무 처리, 기록 보존, 조회와 집계 요구사항.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="31" customHeight="1">
+    <x:row r="10" ht="55" customHeight="1">
       <x:c r="A10" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4683,7 +5005,7 @@
         <x:v>접근 권한, 운영 제어와 공개 조건.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="31" customHeight="1">
+    <x:row r="11" ht="55" customHeight="1">
       <x:c r="A11" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4694,7 +5016,7 @@
         <x:v>AI 판정, 되묻기, 분석과 설명 생성 요구사항.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="31" customHeight="1">
+    <x:row r="12" ht="55" customHeight="1">
       <x:c r="A12" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4705,7 +5027,7 @@
         <x:v>문제·기준표·생각 유형 등 콘텐츠와 데이터 요구사항.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="31" customHeight="1">
+    <x:row r="13" ht="55" customHeight="1">
       <x:c r="A13" s="90" t="str">
         <x:v>비고</x:v>
       </x:c>
@@ -4716,7 +5038,7 @@
         <x:v>기획서에 근거가 있는 핵심 서비스 요구. 뒤 숫자는 기획서의 장·절 번호이다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="31" customHeight="1">
+    <x:row r="14" ht="55" customHeight="1">
       <x:c r="A14" s="90" t="str">
         <x:v>비고</x:v>
       </x:c>
@@ -4727,7 +5049,7 @@
         <x:v>사용자 요청 영역을 구체화한 설계 제안. 기획서에 없는 화면·예외·운영 세부 사항을 포함하며 팀 검토가 필요하다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="42" customHeight="1">
+    <x:row r="15" ht="55" customHeight="1">
       <x:c r="A15" s="90" t="str">
         <x:v>비고</x:v>
       </x:c>
@@ -4738,7 +5060,7 @@
         <x:v>정책이 다른 항목은 비고와 정책란에 검토 필요로 표시한다. P01~P16은 합의 대상이며, 최초 초안 48개 ID의 현재 대응 위치는 아래 초안 대조 행에서 확인한다. 구현·시험 완료를 뜻하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="42" customHeight="1">
+    <x:row r="16" ht="55" customHeight="1">
       <x:c r="A16" s="90" t="str">
         <x:v>범위</x:v>
       </x:c>
@@ -4746,10 +5068,10 @@
         <x:v>현재 작성 영역</x:v>
       </x:c>
       <x:c r="C16" s="91" t="str">
-        <x:v>기존 140개 항목의 ID를 유지하면서 입력·판정·통계·콘텐츠·동의·평가·배포 세부를 보완하고 모델 학습·설명, 학습 보조, 파일 다운로드와 예시 질문을 추가했다. 운영·결제·알림 요구는 유지한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="42" customHeight="1">
+        <x:v>기존160개 ID를 보존하고5개를 추가했다. 성취기준790개 수집본·기존10미션 재태깅·초안/자동검사/검수·정답형 결과/힌트·저학년 건수·모델 사용조건을 보강했다.35미션·데모 계정·보류 구분과 이전 승인 일정은 유지한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="55" customHeight="1">
       <x:c r="A17" s="90" t="str">
         <x:v>범위</x:v>
       </x:c>
@@ -4757,10 +5079,10 @@
         <x:v>확장 항목</x:v>
       </x:c>
       <x:c r="C17" s="91" t="str">
-        <x:v>STT·TTS, M1·sLLM, 자기 평가 등 최초 초안의 선택 기능은 선택 보완으로 표시한다. 지원 범위와 활성화는 관련 정책을 확정한다. 과거 일정·구현 상태·수량은 현재 실행 결과로 승계하지 않는다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
+        <x:v>STT·sLLM·유료 결제/구독·64미션 확장은 데모 범위에서 제외한다. M1은11/1선택용 비교 후보, TTS는10/30까지 채택 여부 확정. 기능/평가 완료는 실행 증거로 구분한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="55" customHeight="1">
       <x:c r="A18" s="90" t="str">
         <x:v>출처</x:v>
       </x:c>
@@ -4771,7 +5093,7 @@
         <x:v>기획 프로젝트 기획서_사유.docx (제출일 2026-10-22). 1 주제, 2 문제 정의, 3.2 차별점, 4 시스템, 4.1 학습 흐름, 4.2 기술, 5.2 평가, 6 데이터, 6.1 기록, 6.2 준수, 7 역할.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="42" customHeight="1">
+    <x:row r="19" ht="55" customHeight="1">
       <x:c r="A19" s="90" t="str">
         <x:v>출처</x:v>
       </x:c>
@@ -4782,7 +5104,7 @@
         <x:v>[기획]요구사항 정의서_ChessInsight_AI.xlsx. 요구사항 정의서 6개 열, 분류별 셀 병합과 작성 기준 시트 구조를 사용했다. 체스 서비스의 기능·정책은 사고뭉치에 승계하지 않았다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="42" customHeight="1">
+    <x:row r="20" ht="55" customHeight="1">
       <x:c r="A20" s="90" t="str">
         <x:v>출처</x:v>
       </x:c>
@@ -4793,7 +5115,7 @@
         <x:v>2026-10-23 최초 초안의 누락·축약 내용을 반영하고 정책 차이는 검토 필요로 구분하라는 요청. 원본 48개 ID를 기존 또는 신규 항목에 연결하며 같은 기능을 별도 중복 행으로 만들지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="31" customHeight="1">
+    <x:row r="21" ht="55" customHeight="1">
       <x:c r="A21" s="90" t="str">
         <x:v>역할</x:v>
       </x:c>
@@ -4804,7 +5126,7 @@
         <x:v>자신에게 제공된 문제를 풀고 되묻기에 답하며, 본인의 학습 과정과 돌아보기를 확인한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="31" customHeight="1">
+    <x:row r="22" ht="55" customHeight="1">
       <x:c r="A22" s="90" t="str">
         <x:v>역할</x:v>
       </x:c>
@@ -4815,7 +5137,7 @@
         <x:v>연결된 자녀의 학습 기록을 조회하고 대화형 분석과 주간 리포트를 통해 변화를 확인한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
+    <x:row r="23" ht="55" customHeight="1">
       <x:c r="A23" s="90" t="str">
         <x:v>역할</x:v>
       </x:c>
@@ -4826,7 +5148,7 @@
         <x:v>승인된 범위에서 문제를 운영하고 처리 상태를 확인한다. 운영 권한이 학생 원문 기록의 무제한 열람을 의미하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="31" customHeight="1">
+    <x:row r="24" ht="55" customHeight="1">
       <x:c r="A24" s="90" t="str">
         <x:v>공통 기준</x:v>
       </x:c>
@@ -4837,7 +5159,7 @@
         <x:v>기록 수·분모·계산식·기간과 참조 기록을 함께 확인할 수 있게 한다. 기록 부재, 분석 보류와 처리 실패를 구분한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="31" customHeight="1">
+    <x:row r="25" ht="55" customHeight="1">
       <x:c r="A25" s="90" t="str">
         <x:v>공통 기준</x:v>
       </x:c>
@@ -4848,7 +5170,7 @@
         <x:v>관찰된 답변 변화와 사고력 향상 효과를 구분한다. 검증 전 숫자 레벨·등급을 표시하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="42" customHeight="1">
+    <x:row r="26" ht="55" customHeight="1">
       <x:c r="A26" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4856,10 +5178,10 @@
         <x:v>P01 계정·접속</x:v>
       </x:c>
       <x:c r="C26" s="91" t="str">
-        <x:v>[검토 필요] 일반 가입·인증 정책은 미정이다. 최초 초안의 시연 계정·?student= 링크 접속을 유지할지 결정한다. 시연 전용 자격과 기록 범위를 분리하고 URL의 학생 식별값만으로 일반 학습 기록 접근을 허용하지 않는다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="31" customHeight="1">
+        <x:v>데모 가상 계정만 운영하며 실제 아동 가입·공개 가입은 제외. 시연 URL 식별값만으로 기록 권한을 허용하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="55" customHeight="1">
       <x:c r="A27" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4870,7 +5192,7 @@
         <x:v>[미정] 자녀 등록·연결 확인 절차, 다자녀 지원 여부, 자녀 선택과 연결 해제 시 기록 접근 범위를 정한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="57" customHeight="1">
+    <x:row r="28" ht="90" customHeight="1">
       <x:c r="A28" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4878,10 +5200,10 @@
         <x:v>P03 학년·입력</x:v>
       </x:c>
       <x:c r="C28" s="91" t="str">
-        <x:v>[미정] 첫 지원 학년과 입력 틀·STT·TTS 범위를 정한다. 초안의 초1~2·초5~6 및 미션 10개는 과거 시연 기준이다. 보호자 받아쓰기를 별도 기록하고 STT 시범은 동의한 성인 음성만 사용·원음 미저장·판정 제외 조건으로 검토한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="42" customHeight="1">
+        <x:v>35미션 구성과 STT 확장 범위는 유지. 초1~2는 고르기/보호자 받아쓰기·정답형/열린형을 섞고 점수 없이 학부모 건수 기록으로 제공한다. 기존10개는 코드·학년 재태깅 후 사용.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="55" customHeight="1">
       <x:c r="A29" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4889,10 +5211,10 @@
         <x:v>P04 학습 종료</x:v>
       </x:c>
       <x:c r="C29" s="91" t="str">
-        <x:v>[검토 필요] 초안은 모든 단계의 이대로 돌아보기와 고르기 정답 후 즉시 돌아보기를 제공한다. 현행의 되묻기 횟수·종료·돌아보기 필수 여부 미정 정책과 합의한 뒤 적용하고, 정답 공개는 확정된 마무리 이후로 제한한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="42" customHeight="1">
+        <x:v>닫힌/열린 문항 분기, 초1~2 1회·초3~4 2회·초5~중3 3회 되묻기 상한과 마무리/힌트/정답 공개를 적용한다. 성공한 질문 턴만 세고 재시도는 중복 집계하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="55" customHeight="1">
       <x:c r="A30" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4900,10 +5222,10 @@
         <x:v>P05 이어하기</x:v>
       </x:c>
       <x:c r="C30" s="91" t="str">
-        <x:v>[검토 필요] 답변 초안 자동 저장은 유지한다. 메모는 초안에서 저장하지 않았으나 현행은 저장 대상 결정을 유보했으므로 보관·복원 여부를 별도 합의한다. 메모→답 칸 이동, 초안 저장 시점·충돌·복원·보존 기간을 정한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="42" customHeight="1">
+        <x:v>답변 초안과 메모를 별도 저장/복원한다. 답변/세션/이벤트 버전·저장 실패·동시 편집 충돌·중복 요청·삭제 범위를 API 계약에 명시한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="55" customHeight="1">
       <x:c r="A31" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4914,7 +5236,7 @@
         <x:v>[미정] 한 주의 경계·시간대·생성 시각, 기간을 걸친 학습의 귀속, 재생성 권한과 기존 결과 보존 방식을 정한다. 주간 자동 생성 자체는 기획서의 핵심 요구이다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="42" customHeight="1">
+    <x:row r="32" ht="55" customHeight="1">
       <x:c r="A32" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4925,7 +5247,7 @@
         <x:v>[미정] 관리자 승인 주체, 작성·검토·공개 권한과 문제 상태 전환 규칙, 오류 조치 권한, 학생 원문 열람의 허용 대상과 목적을 정한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="57" customHeight="1">
+    <x:row r="33" ht="90" customHeight="1">
       <x:c r="A33" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4933,10 +5255,10 @@
         <x:v>P08 집계·모델</x:v>
       </x:c>
       <x:c r="C33" s="91" t="str">
-        <x:v>[검토 필요] 초안의 분모 5 미만은 비율 대신 개수 표시 기준을 유지할지 결정한다. 도움 없이 시작한 비율의 분자·분모·도움 열람 시점과 보호자 받아쓰기 처리, 글자·문장·까닭 연결어의 계산 규칙을 정한다. 모델 세부는 P15와 연결한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="42" customHeight="1">
+        <x:v>초1~2는 모든 표본에서 %/점수/등급/또래 비교 없이 몇 개 중 몇 개만 표시한다. 이유 제시와 보기 사실 일치를 분리한다. 다른 학년의 통계5건 기준·단일 미션 요소수·분모0/보류/실패 구분은 유지.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="55" customHeight="1">
       <x:c r="A34" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -4947,7 +5269,7 @@
         <x:v>[미정] 학습·대화·리포트·운영 이력의 보관 기간과 삭제 절차, 동의 철회 시 처리, 삭제된 근거가 과거 결과에 미치는 영향을 정한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="42" customHeight="1">
+    <x:row r="35" ht="55" customHeight="1">
       <x:c r="A35" s="90" t="str">
         <x:v>연결 관계</x:v>
       </x:c>
@@ -4958,7 +5280,7 @@
         <x:v>기존 이용 흐름과 OPS01·AIO01·PAY01·BIL01·NTF01은 유지한다. MDL01은 모델 학습·설명, STU02는 학습 보조·자기 평가, RPT02는 파일 다운로드, CHT03은 예시 질문을 담당한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="31" customHeight="1">
+    <x:row r="36" ht="55" customHeight="1">
       <x:c r="A36" s="90" t="str">
         <x:v>기능 ID</x:v>
       </x:c>
@@ -4969,7 +5291,7 @@
         <x:v>품질 평가·시나리오 검증·운영 전환 확인. 원본 양식의 평가 분류를 추가 영역에 사용한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="42" customHeight="1">
+    <x:row r="37" ht="55" customHeight="1">
       <x:c r="A37" s="90" t="str">
         <x:v>추가 순위</x:v>
       </x:c>
@@ -4980,7 +5302,7 @@
         <x:v>학습 기록 보존·결과 검토·이용 환경과 운영 안정성의 기반 요구. 추가 그룹 ACC02, FDB01, SAV01, QAS01, UXS01, OPS01, AIO01에 적용한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="42" customHeight="1">
+    <x:row r="38" ht="55" customHeight="1">
       <x:c r="A38" s="90" t="str">
         <x:v>추가 순위</x:v>
       </x:c>
@@ -4988,10 +5310,10 @@
         <x:v>우선 2</x:v>
       </x:c>
       <x:c r="C38" s="91" t="str">
-        <x:v>공개 이용·유료 운영을 위한 삭제, 도움말, 사용자 알림과 결제·구독 요구. DEL01, HLP01, NTF01, PAY01, BIL01에 적용하며 실제 도입 일정은 별도 합의한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="42" customHeight="1">
+        <x:v>결제/구독 관련 DEL01·NTF01·PAY01·BIL01은 보존하되 결제 경로는 데모 이후. 문의/삭제/앱내알림의 데모 범위와 거래 운영 확장을 구분한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="55" customHeight="1">
       <x:c r="A39" s="90" t="str">
         <x:v>용어</x:v>
       </x:c>
@@ -5002,7 +5324,7 @@
         <x:v>사용자 알림은 NTF01에서 한 번만 정의한다. OPS01 경보는 장애·지연·비용 이상을 담당자에게 알리는 운영 사건이며 사용자 알림 목록과 구분한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="42" customHeight="1">
+    <x:row r="40" ht="55" customHeight="1">
       <x:c r="A40" s="90" t="str">
         <x:v>용어</x:v>
       </x:c>
@@ -5013,7 +5335,7 @@
         <x:v>서비스의 환경·배포·상태 감지·로그·장애 복구·백업·비밀정보 관리와 AI 모델·프롬프트의 평가·승인·버전·비용 운영을 뜻한다. 특정 도구·클라우드 도입은 확정하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="42" customHeight="1">
+    <x:row r="41" ht="55" customHeight="1">
       <x:c r="A41" s="90" t="str">
         <x:v>용어</x:v>
       </x:c>
@@ -5024,7 +5346,7 @@
         <x:v>거래의 승인·취소·환불과 구독의 이용 기간·갱신·해지를 구분한다. 확인된 결제 결과를 대상 자녀의 이용 권한에 연결하며 정기 결제 중단과 환불을 구분한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="42" customHeight="1">
+    <x:row r="42" ht="55" customHeight="1">
       <x:c r="A42" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5035,7 +5357,7 @@
         <x:v>[미정] 신고·문의 분류, 담당 권한·처리 목표와 결과 공개 범위, 알림 유형·수신 설정·지원 채널·전달 실패 처리 기준을 정한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="42" customHeight="1">
+    <x:row r="43" ht="90" customHeight="1">
       <x:c r="A43" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5043,10 +5365,10 @@
         <x:v>P11 품질·사용 환경</x:v>
       </x:c>
       <x:c r="C43" s="91" t="str">
-        <x:v>[미정] 기기·브라우저·조작·움직임 줄이기 및 완료 조건을 정한다. 초안의 예시 답안 미션당 20~30개·독립 평가자 2명, 설명 50개 사람 검토는 표본 설계의 검토 기준이며 실제 평가 구성·지연 목표는 합의 후 기록한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="42" customHeight="1">
+        <x:v>대표5미션100답안 독립 카파, M2 보정30~50개/QWK, 되묻기100~200쌍·질문50개·리포트20개·가상4주 기록을 구분한다.35미션×3~5답 시범(105~175개 입력)은 별개 검증이며 전체 타당성 승인으로 확대하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="55" customHeight="1">
       <x:c r="A44" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5054,10 +5376,10 @@
         <x:v>P12 서비스·AI 운영</x:v>
       </x:c>
       <x:c r="C44" s="91" t="str">
-        <x:v>[미정] 배포·복구 승인자, 장애 경보·시간 초과·재시도·사용 한도, 백업 주기·복구 목표, 모델 변경 평가와 활성화·되돌리기 기준을 정한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="42" customHeight="1">
+        <x:v>Docker·EC2·RDS·S3, Kubernetes 제외. 자동 백업7일·배포전스냅샷·주간덤프의 보존/삭제·복구목표는10/30 확정.11/24~25 복원,12/4승인·12/5배포·12/6실제경로·12/7리허설 계획.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="55" customHeight="1">
       <x:c r="A45" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5065,10 +5387,10 @@
         <x:v>P13 결제·구독</x:v>
       </x:c>
       <x:c r="C45" s="91" t="str">
-        <x:v>[미정] PG, 연동·심사 조건, 테스트/실결제 도입 시점, 가격·자녀 수·무료/체험 범위, 청구일·자동 갱신 동의·월말 처리·유예·실패 재청구와 이용 권한을 정한다. 자녀 1명 월 구독은 기획 기준안이다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="42" customHeight="1">
+        <x:v>베이직/플러스/할인은 사업 가설로 보존하되12/7데모는 결제/구독/상품별권한 차등 미연동. PG 테스트 구현·실결제 전환은 재승인 후 별도 일정.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="55" customHeight="1">
       <x:c r="A46" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5076,10 +5398,10 @@
         <x:v>P14 해지·취소·환불</x:v>
       </x:c>
       <x:c r="C46" s="91" t="str">
-        <x:v>[미정] 해지 효력과 잔여 이용 기간, 취소·부분/전액 환불 허용 조건·산정 기준·처리 주체·고지 내용, 권한 회수 시점과 탈퇴·미처리 거래의 관계를 정한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="42" customHeight="1">
+        <x:v>해지·취소·환불은 결제 도입 후 확장. 이번 데모 완료 조건에 포함하지 않으며 미구현을 시험 통과로 표시하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="55" customHeight="1">
       <x:c r="A47" s="90" t="str">
         <x:v>참고 자료</x:v>
       </x:c>
@@ -5090,7 +5412,7 @@
         <x:v>결제 요청과 서버 승인 확인 흐름의 참고. PG 선정 결정을 뜻하지 않는다. https://docs.tosspayments.com/guides/v2/payment-widget/integration (확인 2026-10-23)</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="42" customHeight="1">
+    <x:row r="48" ht="55" customHeight="1">
       <x:c r="A48" s="90" t="str">
         <x:v>참고 자료</x:v>
       </x:c>
@@ -5101,7 +5423,7 @@
         <x:v>자동결제와 구독 청구·해지 흐름 참고. 실제 도입은 선정 PG의 지원·계약 조건을 확인한다. https://docs.tosspayments.com/guides/v2/billing (확인 2026-10-23)</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="42" customHeight="1">
+    <x:row r="49" ht="55" customHeight="1">
       <x:c r="A49" s="90" t="str">
         <x:v>참고 자료</x:v>
       </x:c>
@@ -5112,7 +5434,7 @@
         <x:v>PG 상태 변경 통지와 거래 상태 확인 흐름 참고. 구체적인 진위 확인·재전송 처리는 선정 PG에 맞춰 설계한다. https://docs.tosspayments.com/guides/v2/webhook (확인 2026-10-23)</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="42" customHeight="1">
+    <x:row r="50" ht="55" customHeight="1">
       <x:c r="A50" s="90" t="str">
         <x:v>완료 조건</x:v>
       </x:c>
@@ -5123,7 +5445,7 @@
         <x:v>기존 계정·자녀 연결을 유지한 접근 복구, 저장 실패와 재접속 복원, 신고 접수·검토·정정 이력 연결을 확인한다. 단순 화면 이동을 완료로 보지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="42" customHeight="1">
+    <x:row r="51" ht="55" customHeight="1">
       <x:c r="A51" s="90" t="str">
         <x:v>완료 조건</x:v>
       </x:c>
@@ -5134,7 +5456,7 @@
         <x:v>배포 버전과 실제 실행 버전, 실패 요청의 추적, 이전 승인 버전 복구 및 백업 복구의 기록 정합성, 모델 변경 전후 평가 결과를 확인한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="42" customHeight="1">
+    <x:row r="52" ht="55" customHeight="1">
       <x:c r="A52" s="90" t="str">
         <x:v>완료 조건</x:v>
       </x:c>
@@ -5145,7 +5467,7 @@
         <x:v>검증된 결제 결과와 자녀 권한의 일치, 중복 청구·중복 권한 부여 방지, 갱신·해지·환불의 반영을 확인한다. 알림 실패가 실제 거래 결과를 바꾸지 않아야 한다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="42" customHeight="1">
+    <x:row r="53" ht="55" customHeight="1">
       <x:c r="A53" s="90" t="str">
         <x:v>검증 구분</x:v>
       </x:c>
@@ -5156,7 +5478,7 @@
         <x:v>요구사항 문서의 내용·연결·표시 검증과 실제 서비스 검증을 구분한다. 모의 응답, PG 테스트 거래, 실제 API·실결제, 원격 CI와 배포 확인의 수행 여부를 각각 남긴다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="42" customHeight="1">
+    <x:row r="54" ht="55" customHeight="1">
       <x:c r="A54" s="90" t="str">
         <x:v>출처</x:v>
       </x:c>
@@ -5167,7 +5489,7 @@
         <x:v>모델배포_요구사항 정의서_사유.xlsx의 시트1, REQ-STU-001~REQ-OPS-002 총 48개를 대조했다. 원본의 구현됨·31개 테스트·일정은 별도 실행 검증 없이 현재 완료 상태로 승계하지 않았다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="57" customHeight="1">
+    <x:row r="55" ht="90" customHeight="1">
       <x:c r="A55" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5175,10 +5497,10 @@
         <x:v>P15 모델 경로·활성화</x:v>
       </x:c>
       <x:c r="C55" s="91" t="str">
-        <x:v>[검토 필요] M2 필수·M1 비교 후보·sLLM 선택의 적용 범위와 활성화 기준을 정한다. klue/roberta·LoRA·RunPod는 초안 후보이고 M1 확신도 0.8은 임시값이다. 모델 미활성·관찰 불일치·실패를 구분하며 평가 후 승인한 범위만 사용한다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="57" customHeight="1">
+        <x:v>M2 우선·M1 비교·sLLM 확장은 유지. xlm-roberta-base 파인튜닝 기준선과 후보 사용조건을 학습 전에 확정한다. 기존 승인 일정10/30기준·11/1선택·11/22준비검토·12/4릴리스승인 후 활성화를 유지한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="60" customHeight="1">
       <x:c r="A56" s="90" t="str">
         <x:v>정책 결정</x:v>
       </x:c>
@@ -5189,7 +5511,7 @@
         <x:v>[검토 필요] 초안의 질문 1회 재생성→중립 질문 은행, 근거 없는 요약→템플릿, 검증 실패/키 부재/API 실패→규칙 답을 허용할지 결정한다. 미합의 상태에서 자동 대체하지 않으며 허용 시 실패 사실·출처(llm/llm_retry/bank 등)·조회 근거를 표시하고 임의 데이터로 실패를 숨기지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="42" customHeight="1">
+    <x:row r="57" ht="55" customHeight="1">
       <x:c r="A57" s="90" t="str">
         <x:v>비고</x:v>
       </x:c>
@@ -5200,7 +5522,7 @@
         <x:v>보완은 기존 기능 행의 세부 확장, 신규는 별도 이용 목적의 추가를 뜻한다. 검토 필요는 초기 정책과 현행의 차이·미정 기준이며 정책 합의 전 확정 동작으로 적용하지 않는다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="42" customHeight="1">
+    <x:row r="58" ht="55" customHeight="1">
       <x:c r="A58" s="90" t="str">
         <x:v>연결 관계</x:v>
       </x:c>
@@ -5737,6 +6059,182 @@
       </x:c>
       <x:c r="C106" s="91" t="str">
         <x:v>[보완] FBN-14, FAC-12 — 엔진/화면 역할 분리·변경 추적, 기술·폴더는 확정하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="90" customHeight="1">
+      <x:c r="A108" s="90" t="str">
+        <x:v>정책 결정</x:v>
+      </x:c>
+      <x:c r="B108" s="90" t="str">
+        <x:v>P17 추천·성장·복귀</x:v>
+      </x:c>
+      <x:c r="C108" s="91" t="str">
+        <x:v>후보2개·부족 시 실제개수·요소3회연속 누락 추천은 유지한다. 같은 성취기준에서는 쉬운→어려운 순서로 제시하고 추천 이유/선택을 저장한다. 통계의5건 조건을 난도 추천에 적용하지 않는다.7일 무활동 복귀 계획값은 유지.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="80" customHeight="1">
+      <x:c r="A109" s="90" t="str">
+        <x:v>정책 결정</x:v>
+      </x:c>
+      <x:c r="B109" s="90" t="str">
+        <x:v>P18 쓰기 집계</x:v>
+      </x:c>
+      <x:c r="C109" s="91" t="str">
+        <x:v>10초 이상 입력 중단 횟수(pause_count)·고친횟수·삭제글자수·paste_flag만 집계한다. 포커스이탈/백그라운드·IME·받아쓰기·0/미수집·중복재전송을 구분한다. 임계값은 구현 계획값이며 원문키/클립보드 내용 미저장.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="80" customHeight="1">
+      <x:c r="A110" s="90" t="str">
+        <x:v>역할</x:v>
+      </x:c>
+      <x:c r="B110" s="90" t="str">
+        <x:v>단일 주담당·협업</x:v>
+      </x:c>
+      <x:c r="C110" s="91" t="str">
+        <x:v>WBS 주담당1명을 책임자로 두고 협업 역할을 완료조건에 분리한다. 모호한 항목 조정은 사용자 김동섭. 독립 평가2인 김태윤·황수빈은 상대/모델 결과를 보기 전 판정한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="80" customHeight="1">
+      <x:c r="A111" s="90" t="str">
+        <x:v>일정</x:v>
+      </x:c>
+      <x:c r="B111" s="90" t="str">
+        <x:v>앞당긴 내부 마감</x:v>
+      </x:c>
+      <x:c r="C111" s="91" t="str">
+        <x:v>10/30설계/평가기준,11/18구현/설정/테스트코드,11/19최종검증시작,11/26~12/3수정,12/4승인,12/5배포,12/6경로,12/7리허설,12/8제출. 주말 포함.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="80" customHeight="1">
+      <x:c r="A112" s="90" t="str">
+        <x:v>표본</x:v>
+      </x:c>
+      <x:c r="B112" s="90" t="str">
+        <x:v>대표 평가와 서비스 범위</x:v>
+      </x:c>
+      <x:c r="C112" s="91" t="str">
+        <x:v>100답안은 대표5미션×20개이며 나머지30미션까지 승인하지 않는다. 미션별20~30개는 후속 확대 계획이며 이번일정에700~1050개로 자동 확대하지 않는다. 미검증 범위는 기록 중심·판정 보류.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="80" customHeight="1">
+      <x:c r="A113" s="90" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B113" s="90" t="str">
+        <x:v>수치·집계·효과 구분</x:v>
+      </x:c>
+      <x:c r="C113" s="91" t="str">
+        <x:v>생각요소카파·M2 QWK·되묻기적절성·질문정답/인용·리포트문장오류를 분리한다. 팀원가상기록 검증을 실제아동교육효과·모델일반화로 표현하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="80" customHeight="1">
+      <x:c r="A114" s="90" t="str">
+        <x:v>변경 이력</x:v>
+      </x:c>
+      <x:c r="B114" s="90" t="str">
+        <x:v>2026-10-25 v0.4</x:v>
+      </x:c>
+      <x:c r="C114" s="91" t="str">
+        <x:v>기존151개 ID보존+FFJ-41/42,FBF-38/39,FFH-22,FAC-17,FAD-07,FAR-07/08 추가. PDF의11/22활성화는 준비검토로 변경하고 평가/릴리스 승인후 활성화.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="80" customHeight="1">
+      <x:c r="A115" s="90" t="str">
+        <x:v>출처</x:v>
+      </x:c>
+      <x:c r="B115" s="90" t="str">
+        <x:v>기획서·데이터 보고서</x:v>
+      </x:c>
+      <x:c r="C115" s="91" t="str">
+        <x:v>프로젝트_기획서_사고뭉치_최종_1025_v3.pdf(2.6/3.10/4/5/7), 수집데이터_보고서_사고뭉치_최종_1025_v2.pdf(1/3.1/3.5/4/5).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="80" customHeight="1">
+      <x:c r="A116" s="90" t="str">
+        <x:v>출처</x:v>
+      </x:c>
+      <x:c r="B116" s="90" t="str">
+        <x:v>사용자·멘토링</x:v>
+      </x:c>
+      <x:c r="C116" s="91" t="str">
+        <x:v>2026-10-25 사용자 수정 승인·성함 김동섭·주말허용·완료율보류. https://app.notion.com/p/40280f0d4a6f81e98049e84618356aae</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="80" customHeight="1">
+      <x:c r="A117" s="90" t="str">
+        <x:v>데이터</x:v>
+      </x:c>
+      <x:c r="B117" s="90" t="str">
+        <x:v>단위·모델학습 반입</x:v>
+      </x:c>
+      <x:c r="C117" s="91" t="str">
+        <x:v>AI Hub144,805는 문항·답안 등 서로 다른 단위의 합계로 학습 표본 수로 쓰지 않는다. 데이터별 문항/답안/분할/학습행 수를 모델 보고서에 기록한다. 미션 초안 생성과 모델학습 자료 반입은 분리한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="90" customHeight="1">
+      <x:c r="A119" s="90" t="str">
+        <x:v>정책 결정</x:v>
+      </x:c>
+      <x:c r="B119" s="90" t="str">
+        <x:v>P19 미션 제작·공개</x:v>
+      </x:c>
+      <x:c r="C119" s="91" t="str">
+        <x:v>성취기준790개 수집 보고→정리/원문대조→기존10개 재태깅→LLM초안→자동검사→APM검수→최종 시범/평가→공개 순서를 구분한다. 학년별 질문길이·재생성상한·상태enum은10/30 김동섭이 조정. 자동검사 통과는 공개 승인 아님.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="90" customHeight="1">
+      <x:c r="A120" s="90" t="str">
+        <x:v>정책 결정</x:v>
+      </x:c>
+      <x:c r="B120" s="90" t="str">
+        <x:v>P20 저학년 기록</x:v>
+      </x:c>
+      <x:c r="C120" s="91" t="str">
+        <x:v>choice_result/hint_step과 입력/미션/답변 버전을 연결한다. 처음맞힘/전체정답형·힌트후맞힘/처음틀림·이유제시/전체열린형을 건수로 표시하며 이유의 사실일치는 따로 센다. 분모0은대상없음, 실패/미수집과0을 분리한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="90" customHeight="1">
+      <x:c r="A121" s="90" t="str">
+        <x:v>정책 결정</x:v>
+      </x:c>
+      <x:c r="B121" s="90" t="str">
+        <x:v>P21 모델 사용조건</x:v>
+      </x:c>
+      <x:c r="C121" s="91" t="str">
+        <x:v>김재현이10/28까지 후보별 모델카드·가중치/원저장소·학습/배포 조건·리비전을 확인한다. 미확인 후보는 보류하고 확인된 대체 후보를 비교한다. PDF의MIT/CC표기는 원문확인 출발점이며 법적 적합성 확정으로 다루지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="90" customHeight="1">
+      <x:c r="A122" s="90" t="str">
+        <x:v>변경 이력</x:v>
+      </x:c>
+      <x:c r="B122" s="90" t="str">
+        <x:v>2026-10-26 v0.5</x:v>
+      </x:c>
+      <x:c r="C122" s="91" t="str">
+        <x:v>기존160개ID 보존+FAD-08/FAC-18/FAR-09/FBF-40/FBN-26 추가. 성취기준 수집상태·미션 제작·신규 필드·저학년 집계·동일성취기준 난도 추천·모델 사용조건 반영. 과거 기록과 승인 마감/보류 분리 유지.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="90" customHeight="1">
+      <x:c r="A123" s="90" t="str">
+        <x:v>출처</x:v>
+      </x:c>
+      <x:c r="B123" s="90" t="str">
+        <x:v>기획서·수집 데이터 v4</x:v>
+      </x:c>
+      <x:c r="C123" s="91" t="str">
+        <x:v>프로젝트_기획서_사고뭉치_1025_최종_v4.pdf(4.2/5/6.2/7), 수집데이터_보고서_사고뭉치_1025_최종_v4.pdf(1/3.1/3.5/4/5). 문서의 수집/구현 보고를 실제 실행 검증으로 승계하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="90" customHeight="1">
+      <x:c r="A124" s="90" t="str">
+        <x:v>검증 구분</x:v>
+      </x:c>
+      <x:c r="B124" s="90" t="str">
+        <x:v>콘텐츠 자동검사와 개발 시험</x:v>
+      </x:c>
+      <x:c r="C124" s="91" t="str">
+        <x:v>자동검사는 제공할 기능의 동작 계약이다. 구현 중 서비스 테스트를 반복 실행하지 않고 코드/설정/테스트/평가자료 완료 후 최종단계에서 자동검사 기능·미션 시범·E2E를 함께 검증한다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
